--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -4745,10 +4745,10 @@
         <v>43.8</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>0</v>
@@ -9273,10 +9273,10 @@
         <v>43.8</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L90" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M90" s="7" t="n">
         <v>0</v>
@@ -10114,10 +10114,10 @@
         <v>43.8</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M99" s="7" t="n">
         <v>0</v>
@@ -14775,10 +14775,10 @@
         <v>43.8</v>
       </c>
       <c r="K148" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L148" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M148" s="7" t="n">
         <v>0</v>
@@ -17253,13 +17253,13 @@
         <v>60.1</v>
       </c>
       <c r="K174" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L174" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M174" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N174" s="7" t="n">
         <v>0</v>
@@ -18203,10 +18203,10 @@
         <v>43.8</v>
       </c>
       <c r="K184" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L184" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M184" s="7" t="n">
         <v>0</v>
@@ -19331,10 +19331,10 @@
         <v>43.8</v>
       </c>
       <c r="K196" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L196" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M196" s="7" t="n">
         <v>0</v>
@@ -19707,10 +19707,10 @@
         <v>43.8</v>
       </c>
       <c r="K200" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L200" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M200" s="7" t="n">
         <v>0</v>
@@ -20277,10 +20277,10 @@
         <v>43.8</v>
       </c>
       <c r="K206" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L206" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M206" s="7" t="n">
         <v>0</v>
@@ -22852,10 +22852,10 @@
         <v>43.8</v>
       </c>
       <c r="K233" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L233" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M233" s="7" t="n">
         <v>0</v>
@@ -27820,13 +27820,13 @@
         <v>136.5</v>
       </c>
       <c r="K285" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L285" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M285" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N285" s="7" t="n">
         <v>0</v>
@@ -28750,13 +28750,13 @@
         <v>90</v>
       </c>
       <c r="K295" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L295" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M295" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N295" s="7" t="n">
         <v>0</v>
@@ -28843,13 +28843,13 @@
         <v>90</v>
       </c>
       <c r="K296" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L296" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M296" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N296" s="7" t="n">
         <v>0</v>
@@ -28936,13 +28936,13 @@
         <v>90</v>
       </c>
       <c r="K297" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L297" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M297" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N297" s="7" t="n">
         <v>0</v>
@@ -30517,13 +30517,13 @@
         <v>116.2</v>
       </c>
       <c r="K314" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L314" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M314" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N314" s="7" t="n">
         <v>0</v>
@@ -30703,13 +30703,13 @@
         <v>103.4</v>
       </c>
       <c r="K316" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L316" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M316" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N316" s="7" t="n">
         <v>0</v>
@@ -30796,13 +30796,13 @@
         <v>65.8</v>
       </c>
       <c r="K317" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L317" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M317" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N317" s="7" t="n">
         <v>0</v>
@@ -30889,13 +30889,13 @@
         <v>87.09999999999999</v>
       </c>
       <c r="K318" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L318" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M318" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N318" s="7" t="n">
         <v>0</v>
@@ -30982,10 +30982,10 @@
         <v>98.8</v>
       </c>
       <c r="K319" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L319" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M319" s="7" t="n">
         <v>0</v>
@@ -31075,10 +31075,10 @@
         <v>163.7</v>
       </c>
       <c r="K320" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L320" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M320" s="7" t="n">
         <v>0</v>
@@ -31168,13 +31168,13 @@
         <v>78.40000000000001</v>
       </c>
       <c r="K321" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L321" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M321" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N321" s="7" t="n">
         <v>0</v>
@@ -31261,13 +31261,13 @@
         <v>75.3</v>
       </c>
       <c r="K322" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L322" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M322" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N322" s="7" t="n">
         <v>0</v>
@@ -31354,10 +31354,10 @@
         <v>118</v>
       </c>
       <c r="K323" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L323" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M323" s="7" t="n">
         <v>0</v>
@@ -31447,13 +31447,13 @@
         <v>9.4</v>
       </c>
       <c r="K324" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L324" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M324" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N324" s="7" t="n">
         <v>0</v>
@@ -31540,13 +31540,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="K325" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L325" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M325" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N325" s="7" t="n">
         <v>0</v>
@@ -31633,13 +31633,13 @@
         <v>132.9</v>
       </c>
       <c r="K326" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L326" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M326" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N326" s="7" t="n">
         <v>0</v>
@@ -31726,13 +31726,13 @@
         <v>136.6</v>
       </c>
       <c r="K327" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L327" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M327" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N327" s="7" t="n">
         <v>0</v>
@@ -31819,13 +31819,13 @@
         <v>146.8</v>
       </c>
       <c r="K328" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L328" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M328" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N328" s="7" t="n">
         <v>0</v>
@@ -31912,13 +31912,13 @@
         <v>98.09999999999999</v>
       </c>
       <c r="K329" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L329" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M329" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N329" s="7" t="n">
         <v>0</v>
@@ -32005,13 +32005,13 @@
         <v>36.1</v>
       </c>
       <c r="K330" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L330" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M330" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N330" s="7" t="n">
         <v>0</v>
@@ -32098,13 +32098,13 @@
         <v>76</v>
       </c>
       <c r="K331" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L331" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M331" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N331" s="7" t="n">
         <v>0</v>
@@ -32191,10 +32191,10 @@
         <v>178.7</v>
       </c>
       <c r="K332" s="7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L332" s="7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M332" s="7" t="n">
         <v>0</v>
@@ -32284,10 +32284,10 @@
         <v>181.9</v>
       </c>
       <c r="K333" s="7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L333" s="7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M333" s="7" t="n">
         <v>0</v>
@@ -32377,13 +32377,13 @@
         <v>98.5</v>
       </c>
       <c r="K334" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L334" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M334" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N334" s="7" t="n">
         <v>0</v>
@@ -32470,13 +32470,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="K335" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L335" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M335" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N335" s="7" t="n">
         <v>0</v>
@@ -32563,13 +32563,13 @@
         <v>148.2</v>
       </c>
       <c r="K336" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L336" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M336" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N336" s="7" t="n">
         <v>0</v>
@@ -32656,10 +32656,10 @@
         <v>182.3</v>
       </c>
       <c r="K337" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L337" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M337" s="7" t="n">
         <v>0</v>
@@ -32749,13 +32749,13 @@
         <v>131.6</v>
       </c>
       <c r="K338" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L338" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M338" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N338" s="7" t="n">
         <v>0</v>
@@ -32842,13 +32842,13 @@
         <v>167.1</v>
       </c>
       <c r="K339" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L339" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M339" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="N339" s="7" t="n">
         <v>0</v>
@@ -32935,13 +32935,13 @@
         <v>163.4</v>
       </c>
       <c r="K340" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L340" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M340" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N340" s="7" t="n">
         <v>0</v>
@@ -33028,10 +33028,10 @@
         <v>111.2</v>
       </c>
       <c r="K341" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L341" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M341" s="7" t="n">
         <v>0</v>
@@ -33121,13 +33121,13 @@
         <v>86.5</v>
       </c>
       <c r="K342" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L342" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M342" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N342" s="7" t="n">
         <v>0</v>
@@ -33214,13 +33214,13 @@
         <v>78.40000000000001</v>
       </c>
       <c r="K343" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L343" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M343" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N343" s="7" t="n">
         <v>0</v>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="I2" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>60.1</v>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="I3" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>62</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O3" s="7" t="b">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="I4" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>43.8</v>
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="I5" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>0</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="I9" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J9" s="7" t="n">
         <v>64.3</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>0</v>
@@ -1707,19 +1707,19 @@
         </is>
       </c>
       <c r="I10" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>84.7</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>0</v>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J11" s="7" t="n">
         <v>60.1</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="I12" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>60.1</v>
@@ -1994,19 +1994,19 @@
         </is>
       </c>
       <c r="I13" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J13" s="7" t="n">
         <v>46.7</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13" s="7" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="I14" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>61.6</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O14" s="7" t="b">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="I15" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>60.5</v>
@@ -2277,19 +2277,19 @@
         </is>
       </c>
       <c r="I16" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>93.5</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" s="7" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I17" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>60.1</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="I18" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J18" s="7" t="n">
         <v>82.8</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="I19" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J19" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L19" s="7" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O19" s="7" t="b">
         <v>0</v>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="I20" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20" s="7" t="b">
         <v>0</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I21" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J21" s="7" t="n">
         <v>60.1</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="I22" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J22" s="7" t="n">
         <v>46.7</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="I23" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>60.1</v>
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="I24" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J24" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O24" s="7" t="b">
         <v>0</v>
@@ -3130,13 +3130,13 @@
         </is>
       </c>
       <c r="I25" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L25" s="7" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25" s="7" t="b">
         <v>0</v>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="I26" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J26" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L26" s="7" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O26" s="7" t="b">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         </is>
       </c>
       <c r="I27" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J27" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L27" s="7" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O27" s="7" t="b">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="I28" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>60.1</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="I29" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>73.8</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="I30" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>60.1</v>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="I31" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J31" s="7" t="n">
         <v>60.1</v>
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>93.5</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L32" s="7" t="n">
         <v>0</v>
@@ -3808,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O32" s="7" t="b">
         <v>0</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I33" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J33" s="7" t="n">
         <v>46.7</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="I34" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J34" s="7" t="n">
         <v>60.1</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I35" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J35" s="7" t="n">
         <v>77.09999999999999</v>
@@ -4177,19 +4177,19 @@
         </is>
       </c>
       <c r="I36" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J36" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36" s="7" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="I37" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J37" s="7" t="n">
         <v>57.1</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="I38" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J38" s="7" t="n">
         <v>57.1</v>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="I39" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J39" s="7" t="n">
         <v>57.1</v>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="I40" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J40" s="7" t="n">
         <v>60.1</v>
@@ -4646,19 +4646,19 @@
         </is>
       </c>
       <c r="I41" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J41" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N41" s="7" t="n">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="I43" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J43" s="7" t="n">
         <v>60.1</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="I44" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J44" s="7" t="n">
         <v>60.1</v>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="I45" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J45" s="7" t="n">
         <v>43.8</v>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="I46" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J46" s="7" t="n">
         <v>43.8</v>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I47" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J47" s="7" t="n">
         <v>43.8</v>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I48" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J48" s="7" t="n">
         <v>60.1</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="I49" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J49" s="7" t="n">
         <v>43.8</v>
@@ -5511,19 +5511,19 @@
         </is>
       </c>
       <c r="I50" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J50" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N50" s="7" t="n">
         <v>0</v>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="I51" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J51" s="7" t="n">
         <v>26.5</v>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="I52" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J52" s="7" t="n">
         <v>60.5</v>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="I53" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J53" s="7" t="n">
         <v>60.5</v>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="I54" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J54" s="7" t="n">
         <v>26.5</v>
@@ -5984,19 +5984,19 @@
         </is>
       </c>
       <c r="I55" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J55" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N55" s="7" t="n">
         <v>0</v>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="I56" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J56" s="7" t="n">
         <v>57.1</v>
@@ -6170,19 +6170,19 @@
         </is>
       </c>
       <c r="I57" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J57" s="7" t="n">
         <v>62</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N57" s="7" t="n">
         <v>0</v>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="I58" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J58" s="7" t="n">
         <v>73.8</v>
@@ -6356,19 +6356,19 @@
         </is>
       </c>
       <c r="I59" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J59" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N59" s="7" t="n">
         <v>0</v>
@@ -6449,19 +6449,19 @@
         </is>
       </c>
       <c r="I60" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J60" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N60" s="7" t="n">
         <v>0</v>
@@ -6542,19 +6542,19 @@
         </is>
       </c>
       <c r="I61" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J61" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N61" s="7" t="n">
         <v>0</v>
@@ -6635,19 +6635,19 @@
         </is>
       </c>
       <c r="I62" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J62" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L62" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N62" s="7" t="n">
         <v>0</v>
@@ -6728,19 +6728,19 @@
         </is>
       </c>
       <c r="I63" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J63" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63" s="7" t="n">
         <v>0</v>
@@ -6821,19 +6821,19 @@
         </is>
       </c>
       <c r="I64" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J64" s="7" t="n">
         <v>62</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L64" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M64" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N64" s="7" t="n">
         <v>0</v>
@@ -6914,13 +6914,13 @@
         </is>
       </c>
       <c r="I65" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J65" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L65" s="7" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O65" s="7" t="b">
         <v>0</v>
@@ -7007,13 +7007,13 @@
         </is>
       </c>
       <c r="I66" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J66" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L66" s="7" t="n">
         <v>0</v>
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O66" s="7" t="b">
         <v>0</v>
@@ -7193,19 +7193,19 @@
         </is>
       </c>
       <c r="I68" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J68" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L68" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M68" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N68" s="7" t="n">
         <v>0</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="I69" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J69" s="7" t="n">
         <v>55.7</v>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I70" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J70" s="7" t="n">
         <v>55.7</v>
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="I72" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J72" s="7" t="n">
         <v>73.8</v>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="I73" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J73" s="7" t="n">
         <v>73.8</v>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="I74" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J74" s="7" t="n">
         <v>43.8</v>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I75" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J75" s="7" t="n">
         <v>43.8</v>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I76" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J76" s="7" t="n">
         <v>73.8</v>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="I78" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J78" s="7" t="n">
         <v>43.8</v>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="I79" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J79" s="7" t="n">
         <v>43.8</v>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="I80" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J80" s="7" t="n">
         <v>43.8</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="I81" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J81" s="7" t="n">
         <v>43.8</v>
@@ -8519,7 +8519,7 @@
         </is>
       </c>
       <c r="I82" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J82" s="7" t="n">
         <v>57.1</v>
@@ -8612,19 +8612,19 @@
         </is>
       </c>
       <c r="I83" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J83" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N83" s="7" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I84" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J84" s="7" t="n">
         <v>73.8</v>
@@ -8798,19 +8798,19 @@
         </is>
       </c>
       <c r="I85" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J85" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N85" s="7" t="n">
         <v>0</v>
@@ -8891,19 +8891,19 @@
         </is>
       </c>
       <c r="I86" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J86" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L86" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N86" s="7" t="n">
         <v>0</v>
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="I87" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J87" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L87" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N87" s="7" t="n">
         <v>0</v>
@@ -9077,19 +9077,19 @@
         </is>
       </c>
       <c r="I88" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J88" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L88" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N88" s="7" t="n">
         <v>0</v>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="I89" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J89" s="7" t="n">
         <v>43.8</v>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="I91" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J91" s="7" t="n">
         <v>26.5</v>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="I92" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J92" s="7" t="n">
         <v>43.8</v>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="I93" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J93" s="7" t="n">
         <v>26.5</v>
@@ -9643,19 +9643,19 @@
         </is>
       </c>
       <c r="I94" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J94" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L94" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M94" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N94" s="7" t="n">
         <v>0</v>
@@ -9736,19 +9736,19 @@
         </is>
       </c>
       <c r="I95" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J95" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N95" s="7" t="n">
         <v>0</v>
@@ -9829,19 +9829,19 @@
         </is>
       </c>
       <c r="I96" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J96" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K96" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L96" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M96" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N96" s="7" t="n">
         <v>0</v>
@@ -9922,19 +9922,19 @@
         </is>
       </c>
       <c r="I97" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J97" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N97" s="7" t="n">
         <v>0</v>
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="I98" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J98" s="7" t="n">
         <v>57.6</v>
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="I100" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J100" s="7" t="n">
         <v>26.5</v>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="I101" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J101" s="7" t="n">
         <v>43.8</v>
@@ -10391,19 +10391,19 @@
         </is>
       </c>
       <c r="I102" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J102" s="7" t="n">
         <v>97.59999999999999</v>
       </c>
       <c r="K102" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L102" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M102" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N102" s="7" t="n">
         <v>0</v>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="I103" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J103" s="7" t="n">
         <v>60.5</v>
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="I104" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J104" s="7" t="n">
         <v>60.5</v>
@@ -10682,7 +10682,7 @@
         </is>
       </c>
       <c r="I105" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J105" s="7" t="n">
         <v>19.5</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="I106" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J106" s="7" t="n">
         <v>40.6</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="I107" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J107" s="7" t="n">
         <v>26.5</v>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="I108" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J108" s="7" t="n">
         <v>40.6</v>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="I109" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J109" s="7" t="n">
         <v>79.59999999999999</v>
@@ -11151,19 +11151,19 @@
         </is>
       </c>
       <c r="I110" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J110" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K110" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L110" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M110" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N110" s="7" t="n">
         <v>0</v>
@@ -11244,19 +11244,19 @@
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J111" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M111" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N111" s="7" t="n">
         <v>0</v>
@@ -11337,19 +11337,19 @@
         </is>
       </c>
       <c r="I112" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J112" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K112" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L112" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M112" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N112" s="7" t="n">
         <v>0</v>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="I113" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J113" s="7" t="n">
         <v>60.5</v>
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="I114" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J114" s="7" t="n">
         <v>42.9</v>
@@ -11624,7 +11624,7 @@
         </is>
       </c>
       <c r="I115" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J115" s="7" t="n">
         <v>60.5</v>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="I116" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J116" s="7" t="n">
         <v>40.6</v>
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="I117" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J117" s="7" t="n">
         <v>60.5</v>
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="I118" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J118" s="7" t="n">
         <v>60.5</v>
@@ -12012,7 +12012,7 @@
         </is>
       </c>
       <c r="I119" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J119" s="7" t="n">
         <v>60.5</v>
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="I120" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J120" s="7" t="n">
         <v>40.6</v>
@@ -12206,7 +12206,7 @@
         </is>
       </c>
       <c r="I121" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J121" s="7" t="n">
         <v>42.9</v>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="I122" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J122" s="7" t="n">
         <v>43.8</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="I123" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J123" s="7" t="n">
         <v>40.6</v>
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="I124" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J124" s="7" t="n">
         <v>60.5</v>
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="I125" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J125" s="7" t="n">
         <v>60.5</v>
@@ -12691,7 +12691,7 @@
         </is>
       </c>
       <c r="I126" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J126" s="7" t="n">
         <v>60.5</v>
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="I127" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J127" s="7" t="n">
         <v>73.8</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="I128" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J128" s="7" t="n">
         <v>26.5</v>
@@ -12970,19 +12970,19 @@
         </is>
       </c>
       <c r="I129" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J129" s="7" t="n">
         <v>64.3</v>
       </c>
       <c r="K129" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L129" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M129" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N129" s="7" t="n">
         <v>0</v>
@@ -13067,7 +13067,7 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J130" s="7" t="n">
         <v>60.1</v>
@@ -13164,7 +13164,7 @@
         </is>
       </c>
       <c r="I131" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J131" s="7" t="n">
         <v>60.5</v>
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="I133" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J133" s="7" t="n">
         <v>43.8</v>
@@ -13540,19 +13540,19 @@
         </is>
       </c>
       <c r="I135" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J135" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K135" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L135" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M135" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N135" s="7" t="n">
         <v>0</v>
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="I136" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J136" s="7" t="n">
         <v>73.8</v>
@@ -13726,19 +13726,19 @@
         </is>
       </c>
       <c r="I137" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J137" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K137" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L137" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M137" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N137" s="7" t="n">
         <v>0</v>
@@ -13819,19 +13819,19 @@
         </is>
       </c>
       <c r="I138" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J138" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K138" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L138" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M138" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N138" s="7" t="n">
         <v>0</v>
@@ -13916,7 +13916,7 @@
         </is>
       </c>
       <c r="I139" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J139" s="7" t="n">
         <v>60.5</v>
@@ -14013,7 +14013,7 @@
         </is>
       </c>
       <c r="I140" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J140" s="7" t="n">
         <v>60.5</v>
@@ -14106,19 +14106,19 @@
         </is>
       </c>
       <c r="I141" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J141" s="7" t="n">
         <v>38</v>
       </c>
       <c r="K141" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L141" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M141" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N141" s="7" t="n">
         <v>0</v>
@@ -14199,13 +14199,13 @@
         </is>
       </c>
       <c r="I142" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J142" s="7" t="n">
         <v>64.3</v>
       </c>
       <c r="K142" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L142" s="7" t="n">
         <v>0</v>
@@ -14214,7 +14214,7 @@
         <v>0</v>
       </c>
       <c r="N142" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O142" s="7" t="b">
         <v>0</v>
@@ -14296,7 +14296,7 @@
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J143" s="7" t="n">
         <v>43.8</v>
@@ -14389,19 +14389,19 @@
         </is>
       </c>
       <c r="I144" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J144" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K144" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L144" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M144" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N144" s="7" t="n">
         <v>0</v>
@@ -14486,7 +14486,7 @@
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J145" s="7" t="n">
         <v>43.8</v>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="I146" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J146" s="7" t="n">
         <v>60.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="I149" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J149" s="7" t="n">
         <v>60.5</v>
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="I150" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J150" s="7" t="n">
         <v>60.5</v>
@@ -15056,19 +15056,19 @@
         </is>
       </c>
       <c r="I151" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J151" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K151" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L151" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M151" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N151" s="7" t="n">
         <v>0</v>
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="I152" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J152" s="7" t="n">
         <v>42.9</v>
@@ -15250,7 +15250,7 @@
         </is>
       </c>
       <c r="I153" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J153" s="7" t="n">
         <v>60.5</v>
@@ -15347,7 +15347,7 @@
         </is>
       </c>
       <c r="I154" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J154" s="7" t="n">
         <v>60.5</v>
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="I155" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J155" s="7" t="n">
         <v>40.6</v>
@@ -15541,7 +15541,7 @@
         </is>
       </c>
       <c r="I156" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J156" s="7" t="n">
         <v>60.5</v>
@@ -15638,7 +15638,7 @@
         </is>
       </c>
       <c r="I157" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J157" s="7" t="n">
         <v>42.9</v>
@@ -15735,7 +15735,7 @@
         </is>
       </c>
       <c r="I158" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J158" s="7" t="n">
         <v>60.5</v>
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="I159" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J159" s="7" t="n">
         <v>46.7</v>
@@ -15925,13 +15925,13 @@
         </is>
       </c>
       <c r="I160" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J160" s="7" t="n">
         <v>62</v>
       </c>
       <c r="K160" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L160" s="7" t="n">
         <v>0</v>
@@ -15940,7 +15940,7 @@
         <v>0</v>
       </c>
       <c r="N160" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O160" s="7" t="b">
         <v>0</v>
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="I161" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J161" s="7" t="n">
         <v>42.9</v>
@@ -16115,19 +16115,19 @@
         </is>
       </c>
       <c r="I162" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J162" s="7" t="n">
         <v>62</v>
       </c>
       <c r="K162" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L162" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M162" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N162" s="7" t="n">
         <v>0</v>
@@ -16208,19 +16208,19 @@
         </is>
       </c>
       <c r="I163" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J163" s="7" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="K163" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L163" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M163" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N163" s="7" t="n">
         <v>0</v>
@@ -16301,13 +16301,13 @@
         </is>
       </c>
       <c r="I164" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J164" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K164" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L164" s="7" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
         <v>0</v>
       </c>
       <c r="N164" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O164" s="7" t="b">
         <v>0</v>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="I165" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J165" s="7" t="n">
         <v>73.8</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="I166" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J166" s="7" t="n">
         <v>60.5</v>
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="I167" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J167" s="7" t="n">
         <v>60.5</v>
@@ -16681,13 +16681,13 @@
         </is>
       </c>
       <c r="I168" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J168" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K168" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L168" s="7" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="N168" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O168" s="7" t="b">
         <v>0</v>
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="I169" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J169" s="7" t="n">
         <v>42.9</v>
@@ -16875,7 +16875,7 @@
         </is>
       </c>
       <c r="I170" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J170" s="7" t="n">
         <v>60.1</v>
@@ -16968,7 +16968,7 @@
         </is>
       </c>
       <c r="I171" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J171" s="7" t="n">
         <v>73.8</v>
@@ -17061,19 +17061,19 @@
         </is>
       </c>
       <c r="I172" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J172" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K172" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L172" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M172" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N172" s="7" t="n">
         <v>0</v>
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="I175" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J175" s="7" t="n">
         <v>42.9</v>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="I176" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J176" s="7" t="n">
         <v>60.1</v>
@@ -17534,19 +17534,19 @@
         </is>
       </c>
       <c r="I177" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J177" s="7" t="n">
         <v>59.6</v>
       </c>
       <c r="K177" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L177" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M177" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N177" s="7" t="n">
         <v>0</v>
@@ -17627,19 +17627,19 @@
         </is>
       </c>
       <c r="I178" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J178" s="7" t="n">
         <v>59.6</v>
       </c>
       <c r="K178" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L178" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M178" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N178" s="7" t="n">
         <v>0</v>
@@ -17724,7 +17724,7 @@
         </is>
       </c>
       <c r="I179" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J179" s="7" t="n">
         <v>60.5</v>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="I180" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J180" s="7" t="n">
         <v>60.5</v>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="I182" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J182" s="7" t="n">
         <v>60.5</v>
@@ -18104,19 +18104,19 @@
         </is>
       </c>
       <c r="I183" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J183" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K183" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L183" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M183" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N183" s="7" t="n">
         <v>0</v>
@@ -18290,19 +18290,19 @@
         </is>
       </c>
       <c r="I185" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J185" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K185" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L185" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M185" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N185" s="7" t="n">
         <v>0</v>
@@ -18383,19 +18383,19 @@
         </is>
       </c>
       <c r="I186" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J186" s="7" t="n">
         <v>59.6</v>
       </c>
       <c r="K186" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L186" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M186" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N186" s="7" t="n">
         <v>0</v>
@@ -18476,7 +18476,7 @@
         </is>
       </c>
       <c r="I187" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J187" s="7" t="n">
         <v>73.8</v>
@@ -18569,19 +18569,19 @@
         </is>
       </c>
       <c r="I188" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J188" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K188" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L188" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M188" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N188" s="7" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         </is>
       </c>
       <c r="I189" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J189" s="7" t="n">
         <v>60.5</v>
@@ -18759,19 +18759,19 @@
         </is>
       </c>
       <c r="I190" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J190" s="7" t="n">
         <v>64.3</v>
       </c>
       <c r="K190" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L190" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M190" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N190" s="7" t="n">
         <v>0</v>
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="I191" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J191" s="7" t="n">
         <v>26.5</v>
@@ -18949,7 +18949,7 @@
         </is>
       </c>
       <c r="I192" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J192" s="7" t="n">
         <v>42.9</v>
@@ -19042,19 +19042,19 @@
         </is>
       </c>
       <c r="I193" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J193" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K193" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L193" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M193" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N193" s="7" t="n">
         <v>0</v>
@@ -19135,13 +19135,13 @@
         </is>
       </c>
       <c r="I194" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J194" s="7" t="n">
         <v>64.3</v>
       </c>
       <c r="K194" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L194" s="7" t="n">
         <v>0</v>
@@ -19150,7 +19150,7 @@
         <v>0</v>
       </c>
       <c r="N194" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O194" s="7" t="b">
         <v>0</v>
@@ -19232,7 +19232,7 @@
         </is>
       </c>
       <c r="I195" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J195" s="7" t="n">
         <v>42.9</v>
@@ -19418,19 +19418,19 @@
         </is>
       </c>
       <c r="I197" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J197" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K197" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L197" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M197" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N197" s="7" t="n">
         <v>0</v>
@@ -19511,19 +19511,19 @@
         </is>
       </c>
       <c r="I198" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J198" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K198" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L198" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M198" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N198" s="7" t="n">
         <v>0</v>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="I199" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J199" s="7" t="n">
         <v>60.5</v>
@@ -19798,7 +19798,7 @@
         </is>
       </c>
       <c r="I201" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J201" s="7" t="n">
         <v>60.5</v>
@@ -19895,7 +19895,7 @@
         </is>
       </c>
       <c r="I202" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J202" s="7" t="n">
         <v>60.5</v>
@@ -19992,7 +19992,7 @@
         </is>
       </c>
       <c r="I203" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J203" s="7" t="n">
         <v>60.1</v>
@@ -20085,19 +20085,19 @@
         </is>
       </c>
       <c r="I204" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J204" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K204" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L204" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M204" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N204" s="7" t="n">
         <v>0</v>
@@ -20178,19 +20178,19 @@
         </is>
       </c>
       <c r="I205" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J205" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K205" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L205" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M205" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N205" s="7" t="n">
         <v>0</v>
@@ -20368,7 +20368,7 @@
         </is>
       </c>
       <c r="I207" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J207" s="7" t="n">
         <v>60.5</v>
@@ -20465,7 +20465,7 @@
         </is>
       </c>
       <c r="I208" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J208" s="7" t="n">
         <v>43.8</v>
@@ -20562,7 +20562,7 @@
         </is>
       </c>
       <c r="I209" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J209" s="7" t="n">
         <v>42.9</v>
@@ -20659,7 +20659,7 @@
         </is>
       </c>
       <c r="I210" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J210" s="7" t="n">
         <v>19.5</v>
@@ -20756,7 +20756,7 @@
         </is>
       </c>
       <c r="I211" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J211" s="7" t="n">
         <v>19.5</v>
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="I212" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J212" s="7" t="n">
         <v>19.5</v>
@@ -20950,7 +20950,7 @@
         </is>
       </c>
       <c r="I213" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J213" s="7" t="n">
         <v>42.9</v>
@@ -21043,19 +21043,19 @@
         </is>
       </c>
       <c r="I214" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J214" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K214" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L214" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M214" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N214" s="7" t="n">
         <v>0</v>
@@ -21136,7 +21136,7 @@
         </is>
       </c>
       <c r="I215" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J215" s="7" t="n">
         <v>82.8</v>
@@ -21233,7 +21233,7 @@
         </is>
       </c>
       <c r="I216" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J216" s="7" t="n">
         <v>60.5</v>
@@ -21330,7 +21330,7 @@
         </is>
       </c>
       <c r="I217" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J217" s="7" t="n">
         <v>42.9</v>
@@ -21423,19 +21423,19 @@
         </is>
       </c>
       <c r="I218" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J218" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K218" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L218" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M218" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N218" s="7" t="n">
         <v>0</v>
@@ -21520,7 +21520,7 @@
         </is>
       </c>
       <c r="I219" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J219" s="7" t="n">
         <v>19.5</v>
@@ -21617,7 +21617,7 @@
         </is>
       </c>
       <c r="I220" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J220" s="7" t="n">
         <v>19.5</v>
@@ -21710,19 +21710,19 @@
         </is>
       </c>
       <c r="I221" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J221" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K221" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L221" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M221" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N221" s="7" t="n">
         <v>0</v>
@@ -21807,7 +21807,7 @@
         </is>
       </c>
       <c r="I222" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J222" s="7" t="n">
         <v>60.5</v>
@@ -21900,19 +21900,19 @@
         </is>
       </c>
       <c r="I223" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J223" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K223" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L223" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M223" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N223" s="7" t="n">
         <v>0</v>
@@ -22086,19 +22086,19 @@
         </is>
       </c>
       <c r="I225" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J225" s="7" t="n">
         <v>47.2</v>
       </c>
       <c r="K225" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L225" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M225" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N225" s="7" t="n">
         <v>0</v>
@@ -22183,7 +22183,7 @@
         </is>
       </c>
       <c r="I226" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J226" s="7" t="n">
         <v>60.5</v>
@@ -22280,7 +22280,7 @@
         </is>
       </c>
       <c r="I227" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J227" s="7" t="n">
         <v>60.5</v>
@@ -22377,7 +22377,7 @@
         </is>
       </c>
       <c r="I228" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J228" s="7" t="n">
         <v>60.5</v>
@@ -22474,7 +22474,7 @@
         </is>
       </c>
       <c r="I229" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J229" s="7" t="n">
         <v>60.5</v>
@@ -22567,19 +22567,19 @@
         </is>
       </c>
       <c r="I230" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J230" s="7" t="n">
         <v>93.5</v>
       </c>
       <c r="K230" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L230" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M230" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N230" s="7" t="n">
         <v>0</v>
@@ -22660,19 +22660,19 @@
         </is>
       </c>
       <c r="I231" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J231" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K231" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L231" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M231" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N231" s="7" t="n">
         <v>0</v>
@@ -22753,19 +22753,19 @@
         </is>
       </c>
       <c r="I232" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J232" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K232" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L232" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M232" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N232" s="7" t="n">
         <v>0</v>
@@ -22939,19 +22939,19 @@
         </is>
       </c>
       <c r="I234" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J234" s="7" t="n">
         <v>64.3</v>
       </c>
       <c r="K234" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L234" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M234" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N234" s="7" t="n">
         <v>0</v>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="I235" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J235" s="7" t="n">
         <v>60.5</v>
@@ -23129,19 +23129,19 @@
         </is>
       </c>
       <c r="I236" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J236" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K236" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L236" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M236" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N236" s="7" t="n">
         <v>0</v>
@@ -23226,7 +23226,7 @@
         </is>
       </c>
       <c r="I237" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J237" s="7" t="n">
         <v>60.1</v>
@@ -23323,7 +23323,7 @@
         </is>
       </c>
       <c r="I238" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J238" s="7" t="n">
         <v>46.7</v>
@@ -23420,7 +23420,7 @@
         </is>
       </c>
       <c r="I239" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J239" s="7" t="n">
         <v>46.7</v>
@@ -23513,19 +23513,19 @@
         </is>
       </c>
       <c r="I240" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J240" s="7" t="n">
         <v>93.5</v>
       </c>
       <c r="K240" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L240" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M240" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N240" s="7" t="n">
         <v>0</v>
@@ -23610,7 +23610,7 @@
         </is>
       </c>
       <c r="I241" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J241" s="7" t="n">
         <v>60.1</v>
@@ -23707,7 +23707,7 @@
         </is>
       </c>
       <c r="I242" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J242" s="7" t="n">
         <v>60.5</v>
@@ -23804,7 +23804,7 @@
         </is>
       </c>
       <c r="I243" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J243" s="7" t="n">
         <v>60.1</v>
@@ -23901,7 +23901,7 @@
         </is>
       </c>
       <c r="I244" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J244" s="7" t="n">
         <v>46.7</v>
@@ -23994,7 +23994,7 @@
         </is>
       </c>
       <c r="I245" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J245" s="7" t="n">
         <v>54.8</v>
@@ -24091,7 +24091,7 @@
         </is>
       </c>
       <c r="I246" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J246" s="7" t="n">
         <v>60.1</v>
@@ -24188,7 +24188,7 @@
         </is>
       </c>
       <c r="I247" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J247" s="7" t="n">
         <v>60.1</v>
@@ -24285,7 +24285,7 @@
         </is>
       </c>
       <c r="I248" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J248" s="7" t="n">
         <v>77.09999999999999</v>
@@ -24475,7 +24475,7 @@
         </is>
       </c>
       <c r="I250" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J250" s="7" t="n">
         <v>60.1</v>
@@ -24572,7 +24572,7 @@
         </is>
       </c>
       <c r="I251" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J251" s="7" t="n">
         <v>60.1</v>
@@ -24665,13 +24665,13 @@
         </is>
       </c>
       <c r="I252" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J252" s="7" t="n">
         <v>90.8</v>
       </c>
       <c r="K252" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L252" s="7" t="n">
         <v>0</v>
@@ -24680,7 +24680,7 @@
         <v>0</v>
       </c>
       <c r="N252" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O252" s="7" t="b">
         <v>0</v>
@@ -24762,7 +24762,7 @@
         </is>
       </c>
       <c r="I253" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J253" s="7" t="n">
         <v>60.1</v>
@@ -24859,7 +24859,7 @@
         </is>
       </c>
       <c r="I254" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J254" s="7" t="n">
         <v>77.09999999999999</v>
@@ -24956,7 +24956,7 @@
         </is>
       </c>
       <c r="I255" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J255" s="7" t="n">
         <v>77.09999999999999</v>
@@ -25053,7 +25053,7 @@
         </is>
       </c>
       <c r="I256" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J256" s="7" t="n">
         <v>60.5</v>
@@ -25150,7 +25150,7 @@
         </is>
       </c>
       <c r="I257" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J257" s="7" t="n">
         <v>77.09999999999999</v>
@@ -25247,7 +25247,7 @@
         </is>
       </c>
       <c r="I258" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J258" s="7" t="n">
         <v>77.09999999999999</v>
@@ -25344,7 +25344,7 @@
         </is>
       </c>
       <c r="I259" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J259" s="7" t="n">
         <v>43.8</v>
@@ -25441,7 +25441,7 @@
         </is>
       </c>
       <c r="I260" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J260" s="7" t="n">
         <v>60.1</v>
@@ -25724,7 +25724,7 @@
         </is>
       </c>
       <c r="I263" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J263" s="7" t="n">
         <v>46.7</v>
@@ -25817,7 +25817,7 @@
         </is>
       </c>
       <c r="I264" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J264" s="7" t="n">
         <v>73.8</v>
@@ -25910,7 +25910,7 @@
         </is>
       </c>
       <c r="I265" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J265" s="7" t="n">
         <v>82.8</v>
@@ -26003,19 +26003,19 @@
         </is>
       </c>
       <c r="I266" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J266" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K266" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L266" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M266" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N266" s="7" t="n">
         <v>0</v>
@@ -26096,7 +26096,7 @@
         </is>
       </c>
       <c r="I267" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J267" s="7" t="n">
         <v>54.8</v>
@@ -26189,19 +26189,19 @@
         </is>
       </c>
       <c r="I268" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J268" s="7" t="n">
         <v>61.6</v>
       </c>
       <c r="K268" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L268" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M268" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N268" s="7" t="n">
         <v>0</v>
@@ -26282,19 +26282,19 @@
         </is>
       </c>
       <c r="I269" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J269" s="7" t="n">
         <v>61.6</v>
       </c>
       <c r="K269" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L269" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M269" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N269" s="7" t="n">
         <v>0</v>
@@ -26379,7 +26379,7 @@
         </is>
       </c>
       <c r="I270" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J270" s="7" t="n">
         <v>46.7</v>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="I271" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J271" s="7" t="n">
         <v>46.7</v>
@@ -26573,7 +26573,7 @@
         </is>
       </c>
       <c r="I272" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J272" s="7" t="n">
         <v>46.7</v>
@@ -26670,7 +26670,7 @@
         </is>
       </c>
       <c r="I273" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J273" s="7" t="n">
         <v>60.1</v>
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="I274" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J274" s="7" t="n">
         <v>60.1</v>
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="I275" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J275" s="7" t="n">
         <v>43.8</v>
@@ -26957,7 +26957,7 @@
         </is>
       </c>
       <c r="I276" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J276" s="7" t="n">
         <v>73.8</v>
@@ -27054,7 +27054,7 @@
         </is>
       </c>
       <c r="I277" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J277" s="7" t="n">
         <v>60.1</v>
@@ -27147,13 +27147,13 @@
         </is>
       </c>
       <c r="I278" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J278" s="7" t="n">
         <v>31</v>
       </c>
       <c r="K278" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L278" s="7" t="n">
         <v>0</v>
@@ -27162,7 +27162,7 @@
         <v>0</v>
       </c>
       <c r="N278" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O278" s="7" t="b">
         <v>0</v>
@@ -27244,7 +27244,7 @@
         </is>
       </c>
       <c r="I279" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J279" s="7" t="n">
         <v>60.1</v>
@@ -27341,7 +27341,7 @@
         </is>
       </c>
       <c r="I280" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J280" s="7" t="n">
         <v>60.1</v>
@@ -27438,7 +27438,7 @@
         </is>
       </c>
       <c r="I281" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J281" s="7" t="n">
         <v>40.6</v>
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="I282" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J282" s="7" t="n">
         <v>43.8</v>
@@ -29209,7 +29209,7 @@
         </is>
       </c>
       <c r="I300" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J300" s="7" t="n">
         <v>55.7</v>
@@ -29302,7 +29302,7 @@
         </is>
       </c>
       <c r="I301" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J301" s="7" t="n">
         <v>55.7</v>
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="I302" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J302" s="7" t="n">
         <v>110.3</v>
@@ -29488,7 +29488,7 @@
         </is>
       </c>
       <c r="I303" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J303" s="7" t="n">
         <v>55.7</v>
@@ -29581,7 +29581,7 @@
         </is>
       </c>
       <c r="I304" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J304" s="7" t="n">
         <v>55.7</v>
@@ -29767,7 +29767,7 @@
         </is>
       </c>
       <c r="I306" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J306" s="7" t="n">
         <v>55.7</v>
@@ -29860,19 +29860,19 @@
         </is>
       </c>
       <c r="I307" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J307" s="7" t="n">
         <v>120.5</v>
       </c>
       <c r="K307" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L307" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M307" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N307" s="7" t="n">
         <v>0</v>
@@ -29953,19 +29953,19 @@
         </is>
       </c>
       <c r="I308" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J308" s="7" t="n">
         <v>120.5</v>
       </c>
       <c r="K308" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L308" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M308" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N308" s="7" t="n">
         <v>0</v>
@@ -30046,7 +30046,7 @@
         </is>
       </c>
       <c r="I309" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J309" s="7" t="n">
         <v>110.3</v>
@@ -30139,7 +30139,7 @@
         </is>
       </c>
       <c r="I310" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J310" s="7" t="n">
         <v>55.7</v>
@@ -30232,7 +30232,7 @@
         </is>
       </c>
       <c r="I311" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J311" s="7" t="n">
         <v>140.7</v>
@@ -30325,7 +30325,7 @@
         </is>
       </c>
       <c r="I312" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J312" s="7" t="n">
         <v>55.7</v>
@@ -30418,19 +30418,19 @@
         </is>
       </c>
       <c r="I313" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J313" s="7" t="n">
         <v>120.5</v>
       </c>
       <c r="K313" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L313" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M313" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N313" s="7" t="n">
         <v>0</v>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>54.8</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>0</v>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="I7" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>87.3</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>0</v>
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" s="7" t="b">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="I8" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>87.3</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" s="7" t="b">
         <v>0</v>
@@ -4748,10 +4748,10 @@
         <v>4</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M42" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N42" s="7" t="n">
         <v>0</v>
@@ -7100,19 +7100,19 @@
         </is>
       </c>
       <c r="I67" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J67" s="7" t="n">
         <v>75</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N67" s="7" t="n">
         <v>0</v>
@@ -7472,19 +7472,19 @@
         </is>
       </c>
       <c r="I71" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J71" s="7" t="n">
         <v>75</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N71" s="7" t="n">
         <v>0</v>
@@ -8038,19 +8038,19 @@
         </is>
       </c>
       <c r="I77" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J77" s="7" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N77" s="7" t="n">
         <v>0</v>
@@ -9276,10 +9276,10 @@
         <v>4</v>
       </c>
       <c r="L90" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M90" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N90" s="7" t="n">
         <v>0</v>
@@ -10117,10 +10117,10 @@
         <v>4</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N99" s="7" t="n">
         <v>0</v>
@@ -13257,19 +13257,19 @@
         </is>
       </c>
       <c r="I132" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J132" s="7" t="n">
         <v>93.3</v>
       </c>
       <c r="K132" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L132" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M132" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N132" s="7" t="n">
         <v>0</v>
@@ -13447,19 +13447,19 @@
         </is>
       </c>
       <c r="I134" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J134" s="7" t="n">
         <v>87.3</v>
       </c>
       <c r="K134" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L134" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M134" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N134" s="7" t="n">
         <v>0</v>
@@ -14676,19 +14676,19 @@
         </is>
       </c>
       <c r="I147" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J147" s="7" t="n">
         <v>75</v>
       </c>
       <c r="K147" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L147" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M147" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N147" s="7" t="n">
         <v>0</v>
@@ -14778,10 +14778,10 @@
         <v>4</v>
       </c>
       <c r="L148" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M148" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N148" s="7" t="n">
         <v>0</v>
@@ -17154,19 +17154,19 @@
         </is>
       </c>
       <c r="I173" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J173" s="7" t="n">
         <v>75</v>
       </c>
       <c r="K173" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L173" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M173" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N173" s="7" t="n">
         <v>0</v>
@@ -17914,19 +17914,19 @@
         </is>
       </c>
       <c r="I181" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J181" s="7" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K181" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L181" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M181" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N181" s="7" t="n">
         <v>0</v>
@@ -18206,10 +18206,10 @@
         <v>4</v>
       </c>
       <c r="L184" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M184" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N184" s="7" t="n">
         <v>0</v>
@@ -19334,10 +19334,10 @@
         <v>4</v>
       </c>
       <c r="L196" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M196" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N196" s="7" t="n">
         <v>0</v>
@@ -19710,10 +19710,10 @@
         <v>4</v>
       </c>
       <c r="L200" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M200" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N200" s="7" t="n">
         <v>0</v>
@@ -20280,10 +20280,10 @@
         <v>4</v>
       </c>
       <c r="L206" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M206" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N206" s="7" t="n">
         <v>0</v>
@@ -21993,19 +21993,19 @@
         </is>
       </c>
       <c r="I224" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J224" s="7" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K224" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L224" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M224" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N224" s="7" t="n">
         <v>0</v>
@@ -22855,10 +22855,10 @@
         <v>4</v>
       </c>
       <c r="L233" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M233" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N233" s="7" t="n">
         <v>0</v>
@@ -24378,19 +24378,19 @@
         </is>
       </c>
       <c r="I249" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J249" s="7" t="n">
         <v>93.3</v>
       </c>
       <c r="K249" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L249" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M249" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N249" s="7" t="n">
         <v>0</v>
@@ -25534,19 +25534,19 @@
         </is>
       </c>
       <c r="I261" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J261" s="7" t="n">
         <v>87.3</v>
       </c>
       <c r="K261" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L261" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M261" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N261" s="7" t="n">
         <v>0</v>
@@ -25627,19 +25627,19 @@
         </is>
       </c>
       <c r="I262" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J262" s="7" t="n">
         <v>87.3</v>
       </c>
       <c r="K262" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L262" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M262" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N262" s="7" t="n">
         <v>0</v>
@@ -30985,10 +30985,10 @@
         <v>9</v>
       </c>
       <c r="L319" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M319" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N319" s="7" t="n">
         <v>0</v>
@@ -31078,10 +31078,10 @@
         <v>13</v>
       </c>
       <c r="L320" s="7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M320" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N320" s="7" t="n">
         <v>0</v>
@@ -31357,10 +31357,10 @@
         <v>10</v>
       </c>
       <c r="L323" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M323" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N323" s="7" t="n">
         <v>0</v>
@@ -32194,10 +32194,10 @@
         <v>14</v>
       </c>
       <c r="L332" s="7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M332" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N332" s="7" t="n">
         <v>0</v>
@@ -32287,10 +32287,10 @@
         <v>15</v>
       </c>
       <c r="L333" s="7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M333" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N333" s="7" t="n">
         <v>0</v>
@@ -32659,10 +32659,10 @@
         <v>15</v>
       </c>
       <c r="L337" s="7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M337" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N337" s="7" t="n">
         <v>0</v>
@@ -33031,10 +33031,10 @@
         <v>10</v>
       </c>
       <c r="L341" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M341" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N341" s="7" t="n">
         <v>0</v>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -27628,7 +27628,7 @@
         </is>
       </c>
       <c r="I283" s="7" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J283" s="7" t="n">
         <v>16.2</v>
@@ -27721,7 +27721,7 @@
         </is>
       </c>
       <c r="I284" s="7" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J284" s="7" t="n">
         <v>58.1</v>
@@ -27907,19 +27907,19 @@
         </is>
       </c>
       <c r="I286" s="7" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J286" s="7" t="n">
         <v>157.3</v>
       </c>
       <c r="K286" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L286" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M286" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N286" s="7" t="n">
         <v>0</v>
@@ -28000,7 +28000,7 @@
         </is>
       </c>
       <c r="I287" s="7" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J287" s="7" t="n">
         <v>33.8</v>
@@ -28093,7 +28093,7 @@
         </is>
       </c>
       <c r="I288" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J288" s="7" t="n">
         <v>70</v>
@@ -28186,7 +28186,7 @@
         </is>
       </c>
       <c r="I289" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J289" s="7" t="n">
         <v>70</v>
@@ -28279,7 +28279,7 @@
         </is>
       </c>
       <c r="I290" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J290" s="7" t="n">
         <v>70</v>
@@ -28372,16 +28372,16 @@
         </is>
       </c>
       <c r="I291" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J291" s="7" t="n">
         <v>70.8</v>
       </c>
       <c r="K291" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L291" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M291" s="7" t="n">
         <v>2</v>
@@ -28558,16 +28558,16 @@
         </is>
       </c>
       <c r="I293" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J293" s="7" t="n">
         <v>97.7</v>
       </c>
       <c r="K293" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L293" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M293" s="7" t="n">
         <v>2</v>
@@ -28651,16 +28651,16 @@
         </is>
       </c>
       <c r="I294" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J294" s="7" t="n">
         <v>90</v>
       </c>
       <c r="K294" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L294" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M294" s="7" t="n">
         <v>2</v>
@@ -29023,16 +29023,16 @@
         </is>
       </c>
       <c r="I298" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J298" s="7" t="n">
         <v>75.09999999999999</v>
       </c>
       <c r="K298" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L298" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M298" s="7" t="n">
         <v>2</v>
@@ -29116,16 +29116,16 @@
         </is>
       </c>
       <c r="I299" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J299" s="7" t="n">
         <v>77</v>
       </c>
       <c r="K299" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L299" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M299" s="7" t="n">
         <v>2</v>
@@ -30985,10 +30985,10 @@
         <v>9</v>
       </c>
       <c r="L319" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M319" s="7" t="n">
         <v>5</v>
-      </c>
-      <c r="M319" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N319" s="7" t="n">
         <v>0</v>
@@ -31078,10 +31078,10 @@
         <v>13</v>
       </c>
       <c r="L320" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M320" s="7" t="n">
         <v>7</v>
-      </c>
-      <c r="M320" s="7" t="n">
-        <v>6</v>
       </c>
       <c r="N320" s="7" t="n">
         <v>0</v>
@@ -31357,10 +31357,10 @@
         <v>10</v>
       </c>
       <c r="L323" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M323" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N323" s="7" t="n">
         <v>0</v>
@@ -32194,10 +32194,10 @@
         <v>14</v>
       </c>
       <c r="L332" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M332" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N332" s="7" t="n">
         <v>0</v>
@@ -32287,10 +32287,10 @@
         <v>15</v>
       </c>
       <c r="L333" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M333" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N333" s="7" t="n">
         <v>0</v>
@@ -32659,10 +32659,10 @@
         <v>15</v>
       </c>
       <c r="L337" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M337" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N337" s="7" t="n">
         <v>0</v>
@@ -33031,10 +33031,10 @@
         <v>10</v>
       </c>
       <c r="L341" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M341" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N341" s="7" t="n">
         <v>0</v>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -929,7 +929,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ GADOORA</t>
+          <t>Soura to Gadoora</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ SOURA</t>
+          <t>Jehangir Chowk to Soura</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>SORA ↔ PARIMPORA</t>
+          <t>Sora to Parimpora</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>SORA ↔ LD</t>
+          <t>Sora to LD</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ QAMARWARI</t>
+          <t>Lalbazar to Qamarwari</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ QAMARWARI</t>
+          <t>Soura to Qamarwari</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ HAZRATBAL</t>
+          <t>Qamarwari to Hazratbal</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>SAIDAKADAL ↔ BYPASS</t>
+          <t>Saidakadal to Bypass</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>SAIDAKADAL ↔ BYPASS</t>
+          <t>Saidakadal to Bypass</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ JEHANGIR CHOWK</t>
+          <t>Qamarwari to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JEHANGIR CHOWK</t>
+          <t>Parimpora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>JVC ↔ BATWARA</t>
+          <t>JVC to Batwara</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ BONE JOINT HOSPITAL BARZALLA</t>
+          <t>Hazratbal to Bone Joint Hospital Barzalla</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>GBS ↔ LAL CHOWK</t>
+          <t>GBS to LAL Chowk</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ BAGHI MEHTAB</t>
+          <t>Qamarwari to Baghi Mehtab</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>CHANAPORA ↔ SOURA</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>BATMALOO ↔ DALGATE</t>
+          <t>Batmaloo to Dalgate</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
@@ -15705,7 +15705,7 @@
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ DALGATE</t>
+          <t>Soura to Dalgate</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ CHUNTWALIWAR</t>
+          <t>Soura to Chuntwaliwar</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
@@ -16942,7 +16942,7 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ BATAMALLO</t>
+          <t>Soura to Batamallo</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
@@ -17981,7 +17981,7 @@
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C184" s="7" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="B185" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
@@ -18450,7 +18450,7 @@
       </c>
       <c r="B187" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ DALGATE</t>
+          <t>Rangpora to Dalgate</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
@@ -18919,7 +18919,7 @@
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
@@ -19109,7 +19109,7 @@
       </c>
       <c r="B194" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
@@ -19299,7 +19299,7 @@
       </c>
       <c r="B196" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="B197" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
@@ -19485,7 +19485,7 @@
       </c>
       <c r="B198" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C198" s="7" t="inlineStr">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="B199" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
@@ -19675,7 +19675,7 @@
       </c>
       <c r="B200" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C200" s="7" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="B201" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="B202" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C202" s="7" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="B203" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="B204" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C204" s="7" t="inlineStr">
@@ -20152,7 +20152,7 @@
       </c>
       <c r="B205" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
@@ -20245,7 +20245,7 @@
       </c>
       <c r="B206" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C206" s="7" t="inlineStr">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="B207" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="B208" s="7" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C208" s="7" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="B209" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
@@ -20629,7 +20629,7 @@
       </c>
       <c r="B210" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C210" s="7" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="B211" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="B212" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="B213" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="B214" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="B216" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C216" s="7" t="inlineStr">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="B217" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -21397,7 +21397,7 @@
       </c>
       <c r="B218" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C218" s="7" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="B219" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C220" s="7" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="B221" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="B222" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C222" s="7" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="B223" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -21967,7 +21967,7 @@
       </c>
       <c r="B224" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="B226" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
@@ -22250,7 +22250,7 @@
       </c>
       <c r="B227" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
@@ -22347,7 +22347,7 @@
       </c>
       <c r="B228" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
@@ -22444,7 +22444,7 @@
       </c>
       <c r="B229" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="B230" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
@@ -22634,7 +22634,7 @@
       </c>
       <c r="B231" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="B232" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="B233" s="7" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
@@ -22913,7 +22913,7 @@
       </c>
       <c r="B234" s="7" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C234" s="7" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="B235" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="B236" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C236" s="7" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="B237" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="B238" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C238" s="7" t="inlineStr">
@@ -23390,7 +23390,7 @@
       </c>
       <c r="B239" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C239" s="7" t="inlineStr">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="B240" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C240" s="7" t="inlineStr">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="B241" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="B242" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C242" s="7" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="B243" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C243" s="7" t="inlineStr">
@@ -23871,7 +23871,7 @@
       </c>
       <c r="B244" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="B245" s="7" t="inlineStr">
         <is>
-          <t>MA ROAD ↔ SAFAKADAL</t>
+          <t>Ma Road to Safakadal</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="B246" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C246" s="7" t="inlineStr">
@@ -24158,7 +24158,7 @@
       </c>
       <c r="B247" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C247" s="7" t="inlineStr">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="B248" s="7" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C248" s="7" t="inlineStr">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="B249" s="7" t="inlineStr">
         <is>
-          <t>CHANAPORA ↔ SOURA</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="C249" s="7" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="B250" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C250" s="7" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="B251" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C251" s="7" t="inlineStr">
@@ -24639,7 +24639,7 @@
       </c>
       <c r="B252" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C252" s="7" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="B253" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="B254" s="7" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C254" s="7" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="B255" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LALCHOWK</t>
+          <t>Soura to Lalchowk</t>
         </is>
       </c>
       <c r="C255" s="7" t="inlineStr">
@@ -25023,7 +25023,7 @@
       </c>
       <c r="B256" s="7" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C256" s="7" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="B257" s="7" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="B258" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LALCHOWK</t>
+          <t>Soura to Lalchowk</t>
         </is>
       </c>
       <c r="C258" s="7" t="inlineStr">
@@ -25314,7 +25314,7 @@
       </c>
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="B260" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C260" s="7" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="B261" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
@@ -25601,7 +25601,7 @@
       </c>
       <c r="B262" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C262" s="7" t="inlineStr">
@@ -25694,7 +25694,7 @@
       </c>
       <c r="B263" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -25791,7 +25791,7 @@
       </c>
       <c r="B264" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C264" s="7" t="inlineStr">
@@ -25884,7 +25884,7 @@
       </c>
       <c r="B265" s="7" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="B266" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C266" s="7" t="inlineStr">
@@ -26070,7 +26070,7 @@
       </c>
       <c r="B267" s="7" t="inlineStr">
         <is>
-          <t>MA ROAD ↔ PARIMPORA</t>
+          <t>Ma Road to Parimpora</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="B268" s="7" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="C268" s="7" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="B269" s="7" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
@@ -26349,7 +26349,7 @@
       </c>
       <c r="B270" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C270" s="7" t="inlineStr">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="B271" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="B272" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C272" s="7" t="inlineStr">
@@ -26640,7 +26640,7 @@
       </c>
       <c r="B273" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C273" s="7" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="B274" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C274" s="7" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="B275" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C275" s="7" t="inlineStr">
@@ -26931,7 +26931,7 @@
       </c>
       <c r="B276" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C276" s="7" t="inlineStr">
@@ -27024,7 +27024,7 @@
       </c>
       <c r="B277" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C277" s="7" t="inlineStr">
@@ -27121,7 +27121,7 @@
       </c>
       <c r="B278" s="7" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C278" s="7" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="B279" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C279" s="7" t="inlineStr">
@@ -27311,7 +27311,7 @@
       </c>
       <c r="B280" s="7" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C280" s="7" t="inlineStr">
@@ -27408,7 +27408,7 @@
       </c>
       <c r="B281" s="7" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C281" s="7" t="inlineStr">
@@ -27505,7 +27505,7 @@
       </c>
       <c r="B282" s="7" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C282" s="7" t="inlineStr">
@@ -27602,7 +27602,7 @@
       </c>
       <c r="B283" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to SHANGLIPORA</t>
+          <t>Srinagar to Shanglipora</t>
         </is>
       </c>
       <c r="C283" s="7" t="inlineStr">
@@ -27695,7 +27695,7 @@
       </c>
       <c r="B284" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHEWDARA</t>
+          <t>Srinagar to Chewdara</t>
         </is>
       </c>
       <c r="C284" s="7" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="B285" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHOWKIBAL</t>
+          <t>Srinagar to Chowkibal</t>
         </is>
       </c>
       <c r="C285" s="7" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="B286" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to SAFAPORA SUMBAL</t>
+          <t>Srinagar to Safapora Sumbal</t>
         </is>
       </c>
       <c r="C286" s="7" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="B287" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to URI BARAMULLA</t>
+          <t>Srinagar to URI Baramulla</t>
         </is>
       </c>
       <c r="C287" s="7" t="inlineStr">
@@ -28067,7 +28067,7 @@
       </c>
       <c r="B288" s="7" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="C288" s="7" t="inlineStr">
@@ -28160,7 +28160,7 @@
       </c>
       <c r="B289" s="7" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="C289" s="7" t="inlineStr">
@@ -28253,7 +28253,7 @@
       </c>
       <c r="B290" s="7" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="C290" s="7" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="B291" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BANDIPORA</t>
+          <t>Srinagar to Bandipora</t>
         </is>
       </c>
       <c r="C291" s="7" t="inlineStr">
@@ -28439,7 +28439,7 @@
       </c>
       <c r="B292" s="7" t="inlineStr">
         <is>
-          <t>BANDIPORA to BARAMULLA</t>
+          <t>Bandipora to Baramulla</t>
         </is>
       </c>
       <c r="C292" s="7" t="inlineStr">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="B293" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to ZALOORA</t>
+          <t>Srinagar to Zaloora</t>
         </is>
       </c>
       <c r="C293" s="7" t="inlineStr">
@@ -28625,7 +28625,7 @@
       </c>
       <c r="B294" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BARAMULLA</t>
+          <t>Srinagar to Baramulla</t>
         </is>
       </c>
       <c r="C294" s="7" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="B295" s="7" t="inlineStr">
         <is>
-          <t>KAMALKOTE to BARAMULLA</t>
+          <t>Kamalkote to Baramulla</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
@@ -28811,7 +28811,7 @@
       </c>
       <c r="B296" s="7" t="inlineStr">
         <is>
-          <t>GARKOTE to BARAMULLA</t>
+          <t>Garkote to Baramulla</t>
         </is>
       </c>
       <c r="C296" s="7" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="B297" s="7" t="inlineStr">
         <is>
-          <t>NAMBIA to BARAMULLA</t>
+          <t>Nambia to Baramulla</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
@@ -28997,7 +28997,7 @@
       </c>
       <c r="B298" s="7" t="inlineStr">
         <is>
-          <t>BARAMULA to KUPWRA</t>
+          <t>Baramula to Kupwra</t>
         </is>
       </c>
       <c r="C298" s="7" t="inlineStr">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="B299" s="7" t="inlineStr">
         <is>
-          <t>HARMAN to SRINAGAR</t>
+          <t>Harman to Srinagar</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="B300" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BY PASS</t>
+          <t>Srinagar to By Pass</t>
         </is>
       </c>
       <c r="C300" s="7" t="inlineStr">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="B301" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="B302" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to GULABAGH</t>
+          <t>Srinagar to Gulabagh</t>
         </is>
       </c>
       <c r="C302" s="7" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="B303" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="B304" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C304" s="7" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="B305" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BUCHPORA</t>
+          <t>Srinagar to Buchpora</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
@@ -29741,7 +29741,7 @@
       </c>
       <c r="B306" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C306" s="7" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="B307" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
@@ -29927,7 +29927,7 @@
       </c>
       <c r="B308" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="C308" s="7" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to GULABAGH</t>
+          <t>Srinagar to Gulabagh</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
@@ -30113,7 +30113,7 @@
       </c>
       <c r="B310" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C310" s="7" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="B311" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to GANDERBAL</t>
+          <t>Srinagar to Ganderbal</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
@@ -30299,7 +30299,7 @@
       </c>
       <c r="B312" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C312" s="7" t="inlineStr">
@@ -30392,7 +30392,7 @@
       </c>
       <c r="B313" s="7" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="B331" s="7" t="inlineStr">
         <is>
-          <t>JKPDC Jehangir Chowk to Wadwan</t>
+          <t>Jkpdc Jehangir Chowk to Wadwan</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
@@ -33182,7 +33182,7 @@
       </c>
       <c r="B343" s="7" t="inlineStr">
         <is>
-          <t>Batamaloo to DC Office Budgam</t>
+          <t>Batamaloo to Dc Office Budgam</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -988,7 +988,7 @@
         <v>0.7482</v>
       </c>
       <c r="T2" s="7" t="n">
-        <v>9071</v>
+        <v>11362</v>
       </c>
       <c r="U2" s="7" t="n">
         <v>5.746</v>
@@ -1081,7 +1081,7 @@
         <v>0.0638</v>
       </c>
       <c r="T3" s="7" t="n">
-        <v>8455</v>
+        <v>10590</v>
       </c>
       <c r="U3" s="7" t="n">
         <v>3.4734</v>
@@ -1304,7 +1304,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>FDR-323</t>
+          <t>FDR-320</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
@@ -1328,7 +1328,11 @@
       <c r="F6" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
           <t>LP</t>
@@ -1341,7 +1345,7 @@
         <v>113.3</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>0</v>
@@ -1350,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O6" s="7" t="b">
         <v>0</v>
@@ -1362,13 +1366,13 @@
         <v>0.0125</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S6" s="7" t="n">
         <v>0.0638</v>
       </c>
       <c r="T6" s="7" t="n">
-        <v>8455</v>
+        <v>0</v>
       </c>
       <c r="U6" s="7" t="n">
         <v>3.4734</v>
@@ -1461,7 +1465,7 @@
         <v>0.441</v>
       </c>
       <c r="T7" s="7" t="n">
-        <v>9618</v>
+        <v>12048</v>
       </c>
       <c r="U7" s="7" t="n">
         <v>6.8548</v>
@@ -1554,7 +1558,7 @@
         <v>0.2732</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>16373</v>
+        <v>20509</v>
       </c>
       <c r="U8" s="7" t="n">
         <v>8.305999999999999</v>
@@ -1744,7 +1748,7 @@
         <v>0.7436</v>
       </c>
       <c r="T10" s="7" t="n">
-        <v>9365</v>
+        <v>11731</v>
       </c>
       <c r="U10" s="7" t="n">
         <v>5.422</v>
@@ -1837,7 +1841,7 @@
         <v>0.177</v>
       </c>
       <c r="T11" s="7" t="n">
-        <v>10688</v>
+        <v>13388</v>
       </c>
       <c r="U11" s="7" t="n">
         <v>2.0631</v>
@@ -2027,7 +2031,7 @@
         <v>0.7272</v>
       </c>
       <c r="T13" s="7" t="n">
-        <v>7514</v>
+        <v>9412</v>
       </c>
       <c r="U13" s="7" t="n">
         <v>5.0024</v>
@@ -2056,7 +2060,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>FDR-114</t>
+          <t>FDR-070</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -2066,7 +2070,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -2080,7 +2084,11 @@
       <c r="F14" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
           <t>HP</t>
@@ -2093,7 +2101,7 @@
         <v>86.5</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>0</v>
@@ -2102,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O14" s="7" t="b">
         <v>0</v>
@@ -2114,13 +2122,13 @@
         <v>0.3878</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S14" s="7" t="n">
         <v>0.5865</v>
       </c>
       <c r="T14" s="7" t="n">
-        <v>9863</v>
+        <v>0</v>
       </c>
       <c r="U14" s="7" t="n">
         <v>5.174</v>
@@ -2310,7 +2318,7 @@
         <v>0.5219</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>10836</v>
+        <v>13574</v>
       </c>
       <c r="U16" s="7" t="n">
         <v>3.5932</v>
@@ -2403,7 +2411,7 @@
         <v>0.527</v>
       </c>
       <c r="T17" s="7" t="n">
-        <v>5985</v>
+        <v>7497</v>
       </c>
       <c r="U17" s="7" t="n">
         <v>3.5833</v>
@@ -2496,7 +2504,7 @@
         <v>0.5666</v>
       </c>
       <c r="T18" s="7" t="n">
-        <v>7800</v>
+        <v>9770</v>
       </c>
       <c r="U18" s="7" t="n">
         <v>4.3436</v>
@@ -2589,7 +2597,7 @@
         <v>0.4596</v>
       </c>
       <c r="T19" s="7" t="n">
-        <v>9505</v>
+        <v>11906</v>
       </c>
       <c r="U19" s="7" t="n">
         <v>7.0565</v>
@@ -2779,7 +2787,7 @@
         <v>0.6618000000000001</v>
       </c>
       <c r="T21" s="7" t="n">
-        <v>10674</v>
+        <v>13371</v>
       </c>
       <c r="U21" s="7" t="n">
         <v>5.3087</v>
@@ -3002,7 +3010,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>FDR-114</t>
+          <t>FDR-070</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -3163,7 +3171,7 @@
         <v>0.6232</v>
       </c>
       <c r="T25" s="7" t="n">
-        <v>8301</v>
+        <v>10397</v>
       </c>
       <c r="U25" s="7" t="n">
         <v>7.024</v>
@@ -3353,7 +3361,7 @@
         <v>0.4248</v>
       </c>
       <c r="T27" s="7" t="n">
-        <v>9921</v>
+        <v>12427</v>
       </c>
       <c r="U27" s="7" t="n">
         <v>8.0266</v>
@@ -3382,7 +3390,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>FDR-114</t>
+          <t>FDR-070</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -3576,7 +3584,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>FDR-114</t>
+          <t>FDR-070</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -3673,7 +3681,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>FDR-137</t>
+          <t>FDR-179</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -3683,7 +3691,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
@@ -3697,7 +3705,11 @@
       <c r="F31" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -3710,7 +3722,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L31" s="7" t="n">
         <v>0</v>
@@ -3719,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O31" s="7" t="b">
         <v>0</v>
@@ -3731,13 +3743,13 @@
         <v>0.3539</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S31" s="7" t="n">
         <v>0.4735</v>
       </c>
       <c r="T31" s="7" t="n">
-        <v>9552</v>
+        <v>0</v>
       </c>
       <c r="U31" s="7" t="n">
         <v>7.0908</v>
@@ -3863,7 +3875,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>FDR-114</t>
+          <t>FDR-070</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -4024,7 +4036,7 @@
         <v>0.3906</v>
       </c>
       <c r="T34" s="7" t="n">
-        <v>11337</v>
+        <v>14201</v>
       </c>
       <c r="U34" s="7" t="n">
         <v>5.8913</v>
@@ -4150,7 +4162,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>FDR-008</t>
+          <t>FDR-006</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -4160,7 +4172,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
@@ -4174,7 +4186,11 @@
       <c r="F36" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -4187,7 +4203,7 @@
         <v>115.3</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L36" s="7" t="n">
         <v>0</v>
@@ -4196,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O36" s="7" t="b">
         <v>0</v>
@@ -4208,13 +4224,13 @@
         <v>0.1392</v>
       </c>
       <c r="R36" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S36" s="7" t="n">
         <v>0.3906</v>
       </c>
       <c r="T36" s="7" t="n">
-        <v>11337</v>
+        <v>0</v>
       </c>
       <c r="U36" s="7" t="n">
         <v>5.8913</v>
@@ -4404,7 +4420,7 @@
         <v>0.6744</v>
       </c>
       <c r="T38" s="7" t="n">
-        <v>11785</v>
+        <v>14762</v>
       </c>
       <c r="U38" s="7" t="n">
         <v>5.0155</v>
@@ -4497,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="7" t="n">
-        <v>51299</v>
+        <v>64259</v>
       </c>
       <c r="U39" s="7" t="n">
         <v>1.1425</v>
@@ -4590,7 +4606,7 @@
         <v>0.8004</v>
       </c>
       <c r="T40" s="7" t="n">
-        <v>14266</v>
+        <v>17870</v>
       </c>
       <c r="U40" s="7" t="n">
         <v>4.5541</v>
@@ -4780,7 +4796,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="T42" s="7" t="n">
-        <v>10064</v>
+        <v>12606</v>
       </c>
       <c r="U42" s="7" t="n">
         <v>6.2014</v>
@@ -4970,7 +4986,7 @@
         <v>0.4452</v>
       </c>
       <c r="T44" s="7" t="n">
-        <v>9214</v>
+        <v>11541</v>
       </c>
       <c r="U44" s="7" t="n">
         <v>3.8304</v>
@@ -5160,7 +5176,7 @@
         <v>0.424</v>
       </c>
       <c r="T46" s="7" t="n">
-        <v>11015</v>
+        <v>13798</v>
       </c>
       <c r="U46" s="7" t="n">
         <v>7.3596</v>
@@ -5447,7 +5463,7 @@
         <v>0.6186</v>
       </c>
       <c r="T49" s="7" t="n">
-        <v>7591</v>
+        <v>9509</v>
       </c>
       <c r="U49" s="7" t="n">
         <v>4.6584</v>
@@ -5767,7 +5783,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>FDR-346</t>
+          <t>FDR-345</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -5777,7 +5793,7 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
@@ -5791,7 +5807,11 @@
       <c r="F53" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
           <t>HP</t>
@@ -5804,13 +5824,13 @@
         <v>12.6</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N53" s="7" t="n">
         <v>0</v>
@@ -5825,13 +5845,13 @@
         <v>1</v>
       </c>
       <c r="R53" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T53" s="7" t="n">
-        <v>51299</v>
+        <v>0</v>
       </c>
       <c r="U53" s="7" t="n">
         <v>1.1425</v>
@@ -5924,7 +5944,7 @@
         <v>0.5866</v>
       </c>
       <c r="T54" s="7" t="n">
-        <v>8298</v>
+        <v>10394</v>
       </c>
       <c r="U54" s="7" t="n">
         <v>7.0213</v>
@@ -5953,7 +5973,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>FDR-346</t>
+          <t>FDR-345</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -6050,7 +6070,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>FDR-346</t>
+          <t>FDR-345</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -6147,7 +6167,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>FDR-346</t>
+          <t>FDR-345</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -6308,7 +6328,7 @@
         <v>0.5318000000000001</v>
       </c>
       <c r="T58" s="7" t="n">
-        <v>10506</v>
+        <v>13160</v>
       </c>
       <c r="U58" s="7" t="n">
         <v>6.057</v>
@@ -7177,7 +7197,7 @@
         <v>0.4824</v>
       </c>
       <c r="T67" s="7" t="n">
-        <v>10754</v>
+        <v>13471</v>
       </c>
       <c r="U67" s="7" t="n">
         <v>6.1465</v>
@@ -7206,7 +7226,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>FDR-131</t>
+          <t>FDR-125</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -7216,7 +7236,7 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D68" s="7" t="n">
@@ -7230,7 +7250,11 @@
       <c r="F68" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G68" s="7" t="inlineStr"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -7243,7 +7267,7 @@
         <v>101.2</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L68" s="7" t="n">
         <v>0</v>
@@ -7252,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O68" s="7" t="b">
         <v>0</v>
@@ -7264,13 +7288,13 @@
         <v>0.2771</v>
       </c>
       <c r="R68" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S68" s="7" t="n">
         <v>0.5318000000000001</v>
       </c>
       <c r="T68" s="7" t="n">
-        <v>10506</v>
+        <v>0</v>
       </c>
       <c r="U68" s="7" t="n">
         <v>6.057</v>
@@ -7460,7 +7484,7 @@
         <v>0.2222</v>
       </c>
       <c r="T70" s="7" t="n">
-        <v>10801</v>
+        <v>13529</v>
       </c>
       <c r="U70" s="7" t="n">
         <v>5.2923</v>
@@ -7553,7 +7577,7 @@
         <v>0.6173999999999999</v>
       </c>
       <c r="T71" s="7" t="n">
-        <v>8116</v>
+        <v>10167</v>
       </c>
       <c r="U71" s="7" t="n">
         <v>6.5076</v>
@@ -7582,7 +7606,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>FDR-194</t>
+          <t>FDR-193</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -7592,7 +7616,7 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D72" s="7" t="n">
@@ -7606,7 +7630,11 @@
       <c r="F72" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
           <t>HP</t>
@@ -7619,13 +7647,13 @@
         <v>106.2</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L72" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M72" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N72" s="7" t="n">
         <v>0</v>
@@ -7640,13 +7668,13 @@
         <v>0.4253</v>
       </c>
       <c r="R72" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S72" s="7" t="n">
         <v>0.6173999999999999</v>
       </c>
       <c r="T72" s="7" t="n">
-        <v>8116</v>
+        <v>0</v>
       </c>
       <c r="U72" s="7" t="n">
         <v>6.5076</v>
@@ -7933,7 +7961,7 @@
         <v>0.2762</v>
       </c>
       <c r="T75" s="7" t="n">
-        <v>13603</v>
+        <v>17040</v>
       </c>
       <c r="U75" s="7" t="n">
         <v>5.5881</v>
@@ -8166,7 +8194,7 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>UPGRADED_TO_TRUNK</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D78" s="7" t="n">
@@ -8180,32 +8208,36 @@
       <c r="F78" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="I78" s="7" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J78" s="7" t="n">
         <v>87.2</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P78" s="7" t="n">
         <v>0.4598</v>
@@ -8220,7 +8252,7 @@
         <v>0.2762</v>
       </c>
       <c r="T78" s="7" t="n">
-        <v>13603</v>
+        <v>0</v>
       </c>
       <c r="U78" s="7" t="n">
         <v>5.5881</v>
@@ -8259,7 +8291,7 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>UPGRADED_TO_TRUNK</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D79" s="7" t="n">
@@ -8273,32 +8305,36 @@
       <c r="F79" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="I79" s="7" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J79" s="7" t="n">
         <v>87.2</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P79" s="7" t="n">
         <v>0.4598</v>
@@ -8313,7 +8349,7 @@
         <v>0.2762</v>
       </c>
       <c r="T79" s="7" t="n">
-        <v>13603</v>
+        <v>0</v>
       </c>
       <c r="U79" s="7" t="n">
         <v>5.5881</v>
@@ -8449,7 +8485,7 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>UPGRADED_TO_TRUNK</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D81" s="7" t="n">
@@ -8463,32 +8499,36 @@
       <c r="F81" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="I81" s="7" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J81" s="7" t="n">
         <v>101.8</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" s="7" t="n">
         <v>0.5874</v>
@@ -8503,7 +8543,7 @@
         <v>0.4374</v>
       </c>
       <c r="T81" s="7" t="n">
-        <v>9978</v>
+        <v>0</v>
       </c>
       <c r="U81" s="7" t="n">
         <v>5.1108</v>
@@ -8542,7 +8582,7 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>UPGRADED_TO_TRUNK</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D82" s="7" t="n">
@@ -8556,32 +8596,36 @@
       <c r="F82" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="I82" s="7" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J82" s="7" t="n">
         <v>101.8</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L82" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N82" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" s="7" t="n">
         <v>0.5874</v>
@@ -8596,7 +8640,7 @@
         <v>0.4374</v>
       </c>
       <c r="T82" s="7" t="n">
-        <v>9978</v>
+        <v>0</v>
       </c>
       <c r="U82" s="7" t="n">
         <v>5.1108</v>
@@ -8635,7 +8679,7 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>UPGRADED_TO_TRUNK</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D83" s="7" t="n">
@@ -8649,32 +8693,36 @@
       <c r="F83" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="I83" s="7" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J83" s="7" t="n">
         <v>101.8</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83" s="7" t="n">
         <v>0.5874</v>
@@ -8689,7 +8737,7 @@
         <v>0.4374</v>
       </c>
       <c r="T83" s="7" t="n">
-        <v>9978</v>
+        <v>0</v>
       </c>
       <c r="U83" s="7" t="n">
         <v>5.1108</v>
@@ -9009,7 +9057,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -9019,7 +9067,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D87" s="7" t="n">
@@ -9033,7 +9081,11 @@
       <c r="F87" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -9046,13 +9098,13 @@
         <v>106.5</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L87" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N87" s="7" t="n">
         <v>0</v>
@@ -9067,13 +9119,13 @@
         <v>0.274</v>
       </c>
       <c r="R87" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S87" s="7" t="n">
         <v>0.4248</v>
       </c>
       <c r="T87" s="7" t="n">
-        <v>9921</v>
+        <v>0</v>
       </c>
       <c r="U87" s="7" t="n">
         <v>8.0266</v>
@@ -9490,7 +9542,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -9684,7 +9736,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -9694,7 +9746,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D94" s="7" t="n">
@@ -9708,10 +9760,14 @@
       <c r="F94" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="I94" s="7" t="n">
@@ -9721,13 +9777,13 @@
         <v>89.90000000000001</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L94" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M94" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N94" s="7" t="n">
         <v>0</v>
@@ -9742,13 +9798,13 @@
         <v>0.0929</v>
       </c>
       <c r="R94" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S94" s="7" t="n">
         <v>0.2841</v>
       </c>
       <c r="T94" s="7" t="n">
-        <v>14362</v>
+        <v>0</v>
       </c>
       <c r="U94" s="7" t="n">
         <v>5.8992</v>
@@ -10132,7 +10188,7 @@
         <v>0.466</v>
       </c>
       <c r="T98" s="7" t="n">
-        <v>8801</v>
+        <v>11024</v>
       </c>
       <c r="U98" s="7" t="n">
         <v>6.0104</v>
@@ -10258,7 +10314,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -10355,7 +10411,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -10452,7 +10508,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -10807,7 +10863,7 @@
         <v>0.386</v>
       </c>
       <c r="T105" s="7" t="n">
-        <v>7071</v>
+        <v>8857</v>
       </c>
       <c r="U105" s="7" t="n">
         <v>4.7414</v>
@@ -11224,7 +11280,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -11321,7 +11377,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -11515,7 +11571,7 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -11676,7 +11732,7 @@
         <v>0.3943</v>
       </c>
       <c r="T114" s="7" t="n">
-        <v>6923</v>
+        <v>8671</v>
       </c>
       <c r="U114" s="7" t="n">
         <v>4.643</v>
@@ -11802,7 +11858,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -11963,7 +12019,7 @@
         <v>0.549</v>
       </c>
       <c r="T117" s="7" t="n">
-        <v>7720</v>
+        <v>9671</v>
       </c>
       <c r="U117" s="7" t="n">
         <v>6.1122</v>
@@ -11992,7 +12048,7 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>FDR-111</t>
+          <t>FDR-108</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
@@ -12002,7 +12058,7 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D118" s="7" t="n">
@@ -12016,7 +12072,11 @@
       <c r="F118" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G118" s="7" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
           <t>HP</t>
@@ -12029,7 +12089,7 @@
         <v>70.8</v>
       </c>
       <c r="K118" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L118" s="7" t="n">
         <v>0</v>
@@ -12038,7 +12098,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O118" s="7" t="b">
         <v>0</v>
@@ -12050,13 +12110,13 @@
         <v>0.3521</v>
       </c>
       <c r="R118" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S118" s="7" t="n">
         <v>0.6186</v>
       </c>
       <c r="T118" s="7" t="n">
-        <v>7591</v>
+        <v>0</v>
       </c>
       <c r="U118" s="7" t="n">
         <v>4.6584</v>
@@ -12246,7 +12306,7 @@
         <v>0.3846</v>
       </c>
       <c r="T120" s="7" t="n">
-        <v>14811</v>
+        <v>18552</v>
       </c>
       <c r="U120" s="7" t="n">
         <v>5.3506</v>
@@ -13245,7 +13305,7 @@
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -13342,7 +13402,7 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -13439,7 +13499,7 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>FDR-209</t>
+          <t>FDR-205</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -13449,7 +13509,7 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D133" s="7" t="n">
@@ -13463,7 +13523,11 @@
       <c r="F133" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G133" s="7" t="inlineStr"/>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -13476,7 +13540,7 @@
         <v>101.1</v>
       </c>
       <c r="K133" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L133" s="7" t="n">
         <v>0</v>
@@ -13485,7 +13549,7 @@
         <v>0</v>
       </c>
       <c r="N133" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O133" s="7" t="b">
         <v>0</v>
@@ -13497,13 +13561,13 @@
         <v>0.302</v>
       </c>
       <c r="R133" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S133" s="7" t="n">
         <v>0.549</v>
       </c>
       <c r="T133" s="7" t="n">
-        <v>7720</v>
+        <v>0</v>
       </c>
       <c r="U133" s="7" t="n">
         <v>6.1122</v>
@@ -13532,7 +13596,7 @@
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -13823,7 +13887,7 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -14308,7 +14372,7 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
@@ -14566,7 +14630,7 @@
         <v>0.732</v>
       </c>
       <c r="T144" s="7" t="n">
-        <v>10350</v>
+        <v>12964</v>
       </c>
       <c r="U144" s="7" t="n">
         <v>8.016299999999999</v>
@@ -14659,7 +14723,7 @@
         <v>0.3574</v>
       </c>
       <c r="T145" s="7" t="n">
-        <v>9692</v>
+        <v>12141</v>
       </c>
       <c r="U145" s="7" t="n">
         <v>4.7253</v>
@@ -14688,7 +14752,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
@@ -14785,7 +14849,7 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -14882,7 +14946,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>FDR-188</t>
+          <t>FDR-186</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -14892,7 +14956,7 @@
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D148" s="7" t="n">
@@ -14906,7 +14970,11 @@
       <c r="F148" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G148" s="7" t="inlineStr"/>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
           <t>LP</t>
@@ -14919,13 +14987,13 @@
         <v>78.90000000000001</v>
       </c>
       <c r="K148" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L148" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M148" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N148" s="7" t="n">
         <v>0</v>
@@ -14940,13 +15008,13 @@
         <v>0.1234</v>
       </c>
       <c r="R148" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S148" s="7" t="n">
         <v>0.177</v>
       </c>
       <c r="T148" s="7" t="n">
-        <v>10688</v>
+        <v>0</v>
       </c>
       <c r="U148" s="7" t="n">
         <v>2.0631</v>
@@ -15072,7 +15140,7 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -15330,7 +15398,7 @@
         <v>0.3803</v>
       </c>
       <c r="T152" s="7" t="n">
-        <v>8375</v>
+        <v>10490</v>
       </c>
       <c r="U152" s="7" t="n">
         <v>5.617</v>
@@ -15423,7 +15491,7 @@
         <v>0.8052</v>
       </c>
       <c r="T153" s="7" t="n">
-        <v>4843</v>
+        <v>6067</v>
       </c>
       <c r="U153" s="7" t="n">
         <v>2.5893</v>
@@ -15452,7 +15520,7 @@
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -15549,7 +15617,7 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>FDR-092</t>
+          <t>FDR-090</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
@@ -15559,7 +15627,7 @@
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D155" s="7" t="n">
@@ -15573,7 +15641,11 @@
       <c r="F155" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G155" s="7" t="inlineStr"/>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
           <t>HP</t>
@@ -15586,7 +15658,7 @@
         <v>67.5</v>
       </c>
       <c r="K155" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L155" s="7" t="n">
         <v>0</v>
@@ -15595,7 +15667,7 @@
         <v>0</v>
       </c>
       <c r="N155" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O155" s="7" t="b">
         <v>0</v>
@@ -15607,13 +15679,13 @@
         <v>0.4545</v>
       </c>
       <c r="R155" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S155" s="7" t="n">
         <v>0.7272</v>
       </c>
       <c r="T155" s="7" t="n">
-        <v>7514</v>
+        <v>0</v>
       </c>
       <c r="U155" s="7" t="n">
         <v>5.0024</v>
@@ -15739,7 +15811,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>FDR-153</t>
+          <t>FDR-123</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -15749,7 +15821,7 @@
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D157" s="7" t="n">
@@ -15763,7 +15835,11 @@
       <c r="F157" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G157" s="7" t="inlineStr"/>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -15776,7 +15852,7 @@
         <v>66</v>
       </c>
       <c r="K157" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L157" s="7" t="n">
         <v>0</v>
@@ -15785,7 +15861,7 @@
         <v>0</v>
       </c>
       <c r="N157" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O157" s="7" t="b">
         <v>0</v>
@@ -15797,13 +15873,13 @@
         <v>0.2912</v>
       </c>
       <c r="R157" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S157" s="7" t="n">
         <v>0.4662</v>
       </c>
       <c r="T157" s="7" t="n">
-        <v>7057</v>
+        <v>0</v>
       </c>
       <c r="U157" s="7" t="n">
         <v>3.3704</v>
@@ -15896,7 +15972,7 @@
         <v>0.5376</v>
       </c>
       <c r="T158" s="7" t="n">
-        <v>7803</v>
+        <v>9774</v>
       </c>
       <c r="U158" s="7" t="n">
         <v>4.3834</v>
@@ -16022,7 +16098,7 @@
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>FDR-153</t>
+          <t>FDR-123</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -16119,7 +16195,7 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -16701,7 +16777,7 @@
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -17186,7 +17262,7 @@
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>FDR-014</t>
+          <t>FDR-012</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -17196,7 +17272,7 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D172" s="7" t="n">
@@ -17210,7 +17286,11 @@
       <c r="F172" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G172" s="7" t="inlineStr"/>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -17223,7 +17303,7 @@
         <v>89.7</v>
       </c>
       <c r="K172" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L172" s="7" t="n">
         <v>0</v>
@@ -17232,7 +17312,7 @@
         <v>0</v>
       </c>
       <c r="N172" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O172" s="7" t="b">
         <v>0</v>
@@ -17244,13 +17324,13 @@
         <v>0.1523</v>
       </c>
       <c r="R172" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S172" s="7" t="n">
         <v>0.3574</v>
       </c>
       <c r="T172" s="7" t="n">
-        <v>9692</v>
+        <v>0</v>
       </c>
       <c r="U172" s="7" t="n">
         <v>4.7253</v>
@@ -17440,7 +17520,7 @@
         <v>0.4856</v>
       </c>
       <c r="T174" s="7" t="n">
-        <v>5014</v>
+        <v>6281</v>
       </c>
       <c r="U174" s="7" t="n">
         <v>3.6226</v>
@@ -17727,7 +17807,7 @@
         <v>0.6697</v>
       </c>
       <c r="T177" s="7" t="n">
-        <v>7517</v>
+        <v>9416</v>
       </c>
       <c r="U177" s="7" t="n">
         <v>5.6356</v>
@@ -17756,7 +17836,7 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>FDR-153</t>
+          <t>FDR-123</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
@@ -17950,7 +18030,7 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>FDR-014</t>
+          <t>FDR-012</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -18208,7 +18288,7 @@
         <v>0.7685999999999999</v>
       </c>
       <c r="T182" s="7" t="n">
-        <v>9775</v>
+        <v>12244</v>
       </c>
       <c r="U182" s="7" t="n">
         <v>5.6844</v>
@@ -18495,7 +18575,7 @@
         <v>0.3795</v>
       </c>
       <c r="T185" s="7" t="n">
-        <v>9277</v>
+        <v>11620</v>
       </c>
       <c r="U185" s="7" t="n">
         <v>6.9564</v>
@@ -18621,7 +18701,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -19170,7 +19250,7 @@
         <v>0.132</v>
       </c>
       <c r="T192" s="7" t="n">
-        <v>6557</v>
+        <v>8213</v>
       </c>
       <c r="U192" s="7" t="n">
         <v>4.3482</v>
@@ -19199,7 +19279,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -19393,7 +19473,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -19845,7 +19925,7 @@
         <v>0.4179</v>
       </c>
       <c r="T199" s="7" t="n">
-        <v>11026</v>
+        <v>13812</v>
       </c>
       <c r="U199" s="7" t="n">
         <v>8.921900000000001</v>
@@ -20423,7 +20503,7 @@
         <v>0.6244</v>
       </c>
       <c r="T205" s="7" t="n">
-        <v>9645</v>
+        <v>12082</v>
       </c>
       <c r="U205" s="7" t="n">
         <v>7.2316</v>
@@ -20549,7 +20629,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -20646,7 +20726,7 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -20840,7 +20920,7 @@
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>FDR-092</t>
+          <t>FDR-090</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -20937,7 +21017,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -21131,7 +21211,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -21422,7 +21502,7 @@
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>FDR-153</t>
+          <t>FDR-123</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -21713,7 +21793,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -21810,7 +21890,7 @@
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -22004,7 +22084,7 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -22295,7 +22375,7 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>FDR-037</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -22305,7 +22385,7 @@
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D225" s="7" t="n">
@@ -22319,10 +22399,14 @@
       <c r="F225" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G225" s="7" t="inlineStr"/>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H225" s="7" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="I225" s="7" t="n">
@@ -22332,7 +22416,7 @@
         <v>87.2</v>
       </c>
       <c r="K225" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L225" s="7" t="n">
         <v>0</v>
@@ -22341,7 +22425,7 @@
         <v>0</v>
       </c>
       <c r="N225" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O225" s="7" t="b">
         <v>0</v>
@@ -22353,13 +22437,13 @@
         <v>0.0926</v>
       </c>
       <c r="R225" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S225" s="7" t="n">
         <v>0.2762</v>
       </c>
       <c r="T225" s="7" t="n">
-        <v>13603</v>
+        <v>0</v>
       </c>
       <c r="U225" s="7" t="n">
         <v>5.5881</v>
@@ -22679,7 +22763,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -22937,7 +23021,7 @@
         <v>0.6919999999999999</v>
       </c>
       <c r="T231" s="7" t="n">
-        <v>9555</v>
+        <v>11968</v>
       </c>
       <c r="U231" s="7" t="n">
         <v>7.1645</v>
@@ -22966,7 +23050,7 @@
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>FDR-037</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -23160,7 +23244,7 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>FDR-098</t>
+          <t>FDR-096</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -23170,7 +23254,7 @@
       </c>
       <c r="C234" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D234" s="7" t="n">
@@ -23184,7 +23268,11 @@
       <c r="F234" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G234" s="7" t="inlineStr"/>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H234" s="7" t="inlineStr">
         <is>
           <t>HP</t>
@@ -23197,13 +23285,13 @@
         <v>111.7</v>
       </c>
       <c r="K234" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L234" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M234" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N234" s="7" t="n">
         <v>0</v>
@@ -23218,13 +23306,13 @@
         <v>0.5286</v>
       </c>
       <c r="R234" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S234" s="7" t="n">
         <v>0.6919999999999999</v>
       </c>
       <c r="T234" s="7" t="n">
-        <v>9555</v>
+        <v>0</v>
       </c>
       <c r="U234" s="7" t="n">
         <v>7.1645</v>
@@ -23253,7 +23341,7 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>FDR-021</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
@@ -23350,7 +23438,7 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -23447,7 +23535,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -23641,7 +23729,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>FDR-251</t>
+          <t>FDR-250</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -23651,7 +23739,7 @@
       </c>
       <c r="C239" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D239" s="7" t="n">
@@ -23665,7 +23753,11 @@
       <c r="F239" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G239" s="7" t="inlineStr"/>
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -23678,7 +23770,7 @@
         <v>119.1</v>
       </c>
       <c r="K239" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L239" s="7" t="n">
         <v>0</v>
@@ -23687,7 +23779,7 @@
         <v>0</v>
       </c>
       <c r="N239" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O239" s="7" t="b">
         <v>0</v>
@@ -23699,13 +23791,13 @@
         <v>0.2644</v>
       </c>
       <c r="R239" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S239" s="7" t="n">
         <v>0.4179</v>
       </c>
       <c r="T239" s="7" t="n">
-        <v>11026</v>
+        <v>0</v>
       </c>
       <c r="U239" s="7" t="n">
         <v>8.921900000000001</v>
@@ -24025,7 +24117,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>FDR-037</t>
+          <t>SSCL-04</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -24413,7 +24505,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>FDR-105</t>
+          <t>FDR-104</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
@@ -24423,7 +24515,7 @@
       </c>
       <c r="C247" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D247" s="7" t="n">
@@ -24437,7 +24529,11 @@
       <c r="F247" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G247" s="7" t="inlineStr"/>
+      <c r="G247" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H247" s="7" t="inlineStr">
         <is>
           <t>HP</t>
@@ -24450,7 +24546,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="K247" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L247" s="7" t="n">
         <v>0</v>
@@ -24459,7 +24555,7 @@
         <v>0</v>
       </c>
       <c r="N247" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O247" s="7" t="b">
         <v>0</v>
@@ -24471,13 +24567,13 @@
         <v>0.332</v>
       </c>
       <c r="R247" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S247" s="7" t="n">
         <v>0.6618000000000001</v>
       </c>
       <c r="T247" s="7" t="n">
-        <v>10674</v>
+        <v>0</v>
       </c>
       <c r="U247" s="7" t="n">
         <v>5.3087</v>
@@ -25670,7 +25766,7 @@
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -25961,7 +26057,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -26349,7 +26445,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>FDR-275</t>
+          <t>FDR-260</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -26359,7 +26455,7 @@
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D267" s="7" t="n">
@@ -26373,7 +26469,11 @@
       <c r="F267" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G267" s="7" t="inlineStr"/>
+      <c r="G267" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H267" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -26386,7 +26486,7 @@
         <v>79.3</v>
       </c>
       <c r="K267" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L267" s="7" t="n">
         <v>0</v>
@@ -26395,7 +26495,7 @@
         <v>0</v>
       </c>
       <c r="N267" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O267" s="7" t="b">
         <v>0</v>
@@ -26407,13 +26507,13 @@
         <v>0.2311</v>
       </c>
       <c r="R267" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S267" s="7" t="n">
         <v>0.3803</v>
       </c>
       <c r="T267" s="7" t="n">
-        <v>8375</v>
+        <v>0</v>
       </c>
       <c r="U267" s="7" t="n">
         <v>5.617</v>
@@ -27185,7 +27285,7 @@
         <v>0.2764</v>
       </c>
       <c r="T275" s="7" t="n">
-        <v>5927</v>
+        <v>7424</v>
       </c>
       <c r="U275" s="7" t="n">
         <v>4.312</v>
@@ -28572,7 +28672,7 @@
     <row r="290">
       <c r="A290" s="7" t="inlineStr">
         <is>
-          <t>FDR-298</t>
+          <t>FDR-300</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -28582,7 +28682,7 @@
       </c>
       <c r="C290" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D290" s="7" t="n">
@@ -28596,7 +28696,11 @@
       <c r="F290" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G290" s="7" t="inlineStr"/>
+      <c r="G290" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H290" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -28609,7 +28713,7 @@
         <v>100.2</v>
       </c>
       <c r="K290" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L290" s="7" t="n">
         <v>0</v>
@@ -28618,7 +28722,7 @@
         <v>0</v>
       </c>
       <c r="N290" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O290" s="7" t="b">
         <v>0</v>
@@ -28630,13 +28734,13 @@
         <v>0.2227</v>
       </c>
       <c r="R290" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S290" s="7" t="n">
         <v>0.3064</v>
       </c>
       <c r="T290" s="7" t="n">
-        <v>7687</v>
+        <v>0</v>
       </c>
       <c r="U290" s="7" t="n">
         <v>5.7448</v>
@@ -29117,7 +29221,7 @@
         <v>0.5923</v>
       </c>
       <c r="T295" s="7" t="n">
-        <v>8936</v>
+        <v>11193</v>
       </c>
       <c r="U295" s="7" t="n">
         <v>5.0416</v>
@@ -29243,7 +29347,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>FDR-227</t>
+          <t>FDR-225</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -29404,7 +29508,7 @@
         <v>0.6686</v>
       </c>
       <c r="T298" s="7" t="n">
-        <v>11158</v>
+        <v>13977</v>
       </c>
       <c r="U298" s="7" t="n">
         <v>5.8534</v>
@@ -29627,7 +29731,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>FDR-323</t>
+          <t>FDR-320</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -29724,7 +29828,7 @@
     <row r="302">
       <c r="A302" s="7" t="inlineStr">
         <is>
-          <t>FDR-323</t>
+          <t>FDR-320</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -30273,7 +30377,7 @@
         <v>0.7538</v>
       </c>
       <c r="T307" s="7" t="n">
-        <v>6925</v>
+        <v>8675</v>
       </c>
       <c r="U307" s="7" t="n">
         <v>5.1925</v>
@@ -30593,7 +30697,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>FDR-323</t>
+          <t>FDR-320</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -30690,7 +30794,7 @@
     <row r="312">
       <c r="A312" s="7" t="inlineStr">
         <is>
-          <t>FDR-323</t>
+          <t>FDR-320</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -30787,7 +30891,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>FDR-188</t>
+          <t>FDR-186</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -30884,7 +30988,7 @@
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
         <is>
-          <t>FDR-188</t>
+          <t>FDR-186</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -31175,7 +31279,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>FDR-105</t>
+          <t>FDR-104</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -31336,7 +31440,7 @@
         <v>0.412</v>
       </c>
       <c r="T318" s="7" t="n">
-        <v>9313</v>
+        <v>11665</v>
       </c>
       <c r="U318" s="7" t="n">
         <v>7.0982</v>
@@ -31365,7 +31469,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>FDR-134</t>
+          <t>FDR-133</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -31375,7 +31479,7 @@
       </c>
       <c r="C319" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D319" s="7" t="n">
@@ -31389,7 +31493,11 @@
       <c r="F319" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G319" s="7" t="inlineStr"/>
+      <c r="G319" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H319" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -31402,13 +31510,13 @@
         <v>65</v>
       </c>
       <c r="K319" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L319" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M319" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N319" s="7" t="n">
         <v>0</v>
@@ -31423,13 +31531,13 @@
         <v>0.3458</v>
       </c>
       <c r="R319" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S319" s="7" t="n">
         <v>0.527</v>
       </c>
       <c r="T319" s="7" t="n">
-        <v>5985</v>
+        <v>0</v>
       </c>
       <c r="U319" s="7" t="n">
         <v>3.5833</v>
@@ -31458,7 +31566,7 @@
     <row r="320">
       <c r="A320" s="7" t="inlineStr">
         <is>
-          <t>FDR-134</t>
+          <t>FDR-133</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -32428,7 +32536,7 @@
     <row r="330">
       <c r="A330" s="7" t="inlineStr">
         <is>
-          <t>FDR-219</t>
+          <t>FDR-213</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -32438,7 +32546,7 @@
       </c>
       <c r="C330" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D330" s="7" t="n">
@@ -32452,7 +32560,11 @@
       <c r="F330" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G330" s="7" t="inlineStr"/>
+      <c r="G330" s="7" t="inlineStr">
+        <is>
+          <t>LPV / Tempo</t>
+        </is>
+      </c>
       <c r="H330" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -32465,7 +32577,7 @@
         <v>62.1</v>
       </c>
       <c r="K330" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L330" s="7" t="n">
         <v>0</v>
@@ -32474,7 +32586,7 @@
         <v>0</v>
       </c>
       <c r="N330" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O330" s="7" t="b">
         <v>0</v>
@@ -32486,13 +32598,13 @@
         <v>0.2099</v>
       </c>
       <c r="R330" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S330" s="7" t="n">
         <v>0.4856</v>
       </c>
       <c r="T330" s="7" t="n">
-        <v>5014</v>
+        <v>0</v>
       </c>
       <c r="U330" s="7" t="n">
         <v>3.6226</v>
@@ -32812,7 +32924,7 @@
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>FDR-114</t>
+          <t>FDR-070</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -32909,7 +33021,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>FDR-114</t>
+          <t>FDR-070</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -33006,7 +33118,7 @@
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>FDR-211</t>
+          <t>FDR-205</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -33016,7 +33128,7 @@
       </c>
       <c r="C336" s="7" t="inlineStr">
         <is>
-          <t>RETAINED_AS_FEEDER</t>
+          <t>MERGED_INTO_TRUNK</t>
         </is>
       </c>
       <c r="D336" s="7" t="n">
@@ -33030,7 +33142,11 @@
       <c r="F336" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G336" s="7" t="inlineStr"/>
+      <c r="G336" s="7" t="inlineStr">
+        <is>
+          <t>Private Minibus</t>
+        </is>
+      </c>
       <c r="H336" s="7" t="inlineStr">
         <is>
           <t>MP</t>
@@ -33043,13 +33159,13 @@
         <v>101.1</v>
       </c>
       <c r="K336" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L336" s="7" t="n">
         <v>0</v>
       </c>
       <c r="M336" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N336" s="7" t="n">
         <v>0</v>
@@ -33064,13 +33180,13 @@
         <v>0.302</v>
       </c>
       <c r="R336" s="7" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="S336" s="7" t="n">
         <v>0.549</v>
       </c>
       <c r="T336" s="7" t="n">
-        <v>7720</v>
+        <v>0</v>
       </c>
       <c r="U336" s="7" t="n">
         <v>6.1122</v>
@@ -33163,7 +33279,7 @@
         <v>0.0998</v>
       </c>
       <c r="T337" s="7" t="n">
-        <v>8389</v>
+        <v>10508</v>
       </c>
       <c r="U337" s="7" t="n">
         <v>3.9437</v>
@@ -33256,7 +33372,7 @@
         <v>0.241</v>
       </c>
       <c r="T338" s="7" t="n">
-        <v>18565</v>
+        <v>23255</v>
       </c>
       <c r="U338" s="7" t="n">
         <v>11.5301</v>
@@ -33349,7 +33465,7 @@
         <v>0.153</v>
       </c>
       <c r="T339" s="7" t="n">
-        <v>11981</v>
+        <v>15007</v>
       </c>
       <c r="U339" s="7" t="n">
         <v>7.4408</v>
@@ -33442,7 +33558,7 @@
         <v>0.0683</v>
       </c>
       <c r="T340" s="7" t="n">
-        <v>10660</v>
+        <v>13353</v>
       </c>
       <c r="U340" s="7" t="n">
         <v>5.0117</v>
@@ -33535,7 +33651,7 @@
         <v>0.011</v>
       </c>
       <c r="T341" s="7" t="n">
-        <v>14717</v>
+        <v>18435</v>
       </c>
       <c r="U341" s="7" t="n">
         <v>6.9195</v>
@@ -33628,7 +33744,7 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="T342" s="7" t="n">
-        <v>14761</v>
+        <v>18490</v>
       </c>
       <c r="U342" s="7" t="n">
         <v>9.205</v>
@@ -33915,7 +34031,7 @@
         <v>0.0564</v>
       </c>
       <c r="T345" s="7" t="n">
-        <v>32069</v>
+        <v>40170</v>
       </c>
       <c r="U345" s="7" t="n">
         <v>6.666</v>
@@ -34008,7 +34124,7 @@
         <v>0.1472</v>
       </c>
       <c r="T346" s="7" t="n">
-        <v>16857</v>
+        <v>21115</v>
       </c>
       <c r="U346" s="7" t="n">
         <v>10.4693</v>
@@ -34198,7 +34314,7 @@
         <v>0.1353</v>
       </c>
       <c r="T348" s="7" t="n">
-        <v>20320</v>
+        <v>25453</v>
       </c>
       <c r="U348" s="7" t="n">
         <v>9.301600000000001</v>
@@ -34291,7 +34407,7 @@
         <v>0.0209</v>
       </c>
       <c r="T349" s="7" t="n">
-        <v>14489</v>
+        <v>18149</v>
       </c>
       <c r="U349" s="7" t="n">
         <v>6.8123</v>
@@ -34384,7 +34500,7 @@
         <v>0.0164</v>
       </c>
       <c r="T350" s="7" t="n">
-        <v>13482</v>
+        <v>16888</v>
       </c>
       <c r="U350" s="7" t="n">
         <v>6.3388</v>
@@ -34477,7 +34593,7 @@
         <v>0.2224</v>
       </c>
       <c r="T351" s="7" t="n">
-        <v>15410</v>
+        <v>19303</v>
       </c>
       <c r="U351" s="7" t="n">
         <v>7.0542</v>
@@ -34667,7 +34783,7 @@
         <v>0.1926</v>
       </c>
       <c r="T353" s="7" t="n">
-        <v>9750</v>
+        <v>12213</v>
       </c>
       <c r="U353" s="7" t="n">
         <v>4.5593</v>
@@ -34857,7 +34973,7 @@
         <v>0.6908</v>
       </c>
       <c r="T355" s="7" t="n">
-        <v>9610</v>
+        <v>12037</v>
       </c>
       <c r="U355" s="7" t="n">
         <v>4.3998</v>
@@ -34950,7 +35066,7 @@
         <v>0.598</v>
       </c>
       <c r="T356" s="7" t="n">
-        <v>7299</v>
+        <v>9143</v>
       </c>
       <c r="U356" s="7" t="n">
         <v>4.1003</v>
@@ -35237,7 +35353,7 @@
         <v>0.7554999999999999</v>
       </c>
       <c r="T359" s="7" t="n">
-        <v>7437</v>
+        <v>9316</v>
       </c>
       <c r="U359" s="7" t="n">
         <v>5.411</v>
@@ -35330,7 +35446,7 @@
         <v>0.3425</v>
       </c>
       <c r="T360" s="7" t="n">
-        <v>9029</v>
+        <v>11310</v>
       </c>
       <c r="U360" s="7" t="n">
         <v>4.2225</v>
@@ -35423,7 +35539,7 @@
         <v>0.1884</v>
       </c>
       <c r="T361" s="7" t="n">
-        <v>9535</v>
+        <v>11944</v>
       </c>
       <c r="U361" s="7" t="n">
         <v>5.357</v>
@@ -35613,7 +35729,7 @@
         <v>0.1334</v>
       </c>
       <c r="T363" s="7" t="n">
-        <v>14310</v>
+        <v>17925</v>
       </c>
       <c r="U363" s="7" t="n">
         <v>10.4818</v>
@@ -35706,7 +35822,7 @@
         <v>0.4065</v>
       </c>
       <c r="T364" s="7" t="n">
-        <v>13735</v>
+        <v>17205</v>
       </c>
       <c r="U364" s="7" t="n">
         <v>6.5598</v>
@@ -36381,7 +36497,7 @@
         <v>0.2337</v>
       </c>
       <c r="T371" s="7" t="n">
-        <v>10691</v>
+        <v>13391</v>
       </c>
       <c r="U371" s="7" t="n">
         <v>4.2856</v>
@@ -37153,7 +37269,7 @@
         <v>0.4245</v>
       </c>
       <c r="T379" s="7" t="n">
-        <v>8510</v>
+        <v>10659</v>
       </c>
       <c r="U379" s="7" t="n">
         <v>6.1913</v>
@@ -38313,7 +38429,7 @@
         <v>0.4458</v>
       </c>
       <c r="T391" s="7" t="n">
-        <v>11826</v>
+        <v>14814</v>
       </c>
       <c r="U391" s="7" t="n">
         <v>5.7951</v>
@@ -38406,7 +38522,7 @@
         <v>0.427</v>
       </c>
       <c r="T392" s="7" t="n">
-        <v>16981</v>
+        <v>21270</v>
       </c>
       <c r="U392" s="7" t="n">
         <v>10.2523</v>
@@ -38499,7 +38615,7 @@
         <v>0.2059</v>
       </c>
       <c r="T393" s="7" t="n">
-        <v>8908</v>
+        <v>11159</v>
       </c>
       <c r="U393" s="7" t="n">
         <v>2.0059</v>
@@ -38592,7 +38708,7 @@
         <v>0.5696</v>
       </c>
       <c r="T394" s="7" t="n">
-        <v>8763</v>
+        <v>10976</v>
       </c>
       <c r="U394" s="7" t="n">
         <v>5.9623</v>
@@ -38685,7 +38801,7 @@
         <v>0.131</v>
       </c>
       <c r="T395" s="7" t="n">
-        <v>10545</v>
+        <v>13209</v>
       </c>
       <c r="U395" s="7" t="n">
         <v>2.3745</v>
@@ -38778,7 +38894,7 @@
         <v>0.6685</v>
       </c>
       <c r="T396" s="7" t="n">
-        <v>11098</v>
+        <v>13901</v>
       </c>
       <c r="U396" s="7" t="n">
         <v>5.822</v>
@@ -38871,7 +38987,7 @@
         <v>0.2514</v>
       </c>
       <c r="T397" s="7" t="n">
-        <v>11780</v>
+        <v>14756</v>
       </c>
       <c r="U397" s="7" t="n">
         <v>6.1213</v>
@@ -38964,7 +39080,7 @@
         <v>0.1551</v>
       </c>
       <c r="T398" s="7" t="n">
-        <v>34715</v>
+        <v>43485</v>
       </c>
       <c r="U398" s="7" t="n">
         <v>7.216</v>
@@ -39057,7 +39173,7 @@
         <v>0.0848</v>
       </c>
       <c r="T399" s="7" t="n">
-        <v>12352</v>
+        <v>15472</v>
       </c>
       <c r="U399" s="7" t="n">
         <v>2.7817</v>
@@ -39150,7 +39266,7 @@
         <v>0.5037</v>
       </c>
       <c r="T400" s="7" t="n">
-        <v>9695</v>
+        <v>12144</v>
       </c>
       <c r="U400" s="7" t="n">
         <v>6.8851</v>
@@ -39243,7 +39359,7 @@
         <v>0.2336</v>
       </c>
       <c r="T401" s="7" t="n">
-        <v>12979</v>
+        <v>16258</v>
       </c>
       <c r="U401" s="7" t="n">
         <v>6.7445</v>
@@ -39336,7 +39452,7 @@
         <v>0.9247</v>
       </c>
       <c r="T402" s="7" t="n">
-        <v>4621</v>
+        <v>5788</v>
       </c>
       <c r="U402" s="7" t="n">
         <v>1.0634</v>
@@ -39429,7 +39545,7 @@
         <v>0.6467000000000001</v>
       </c>
       <c r="T403" s="7" t="n">
-        <v>11441</v>
+        <v>14332</v>
       </c>
       <c r="U403" s="7" t="n">
         <v>5.6902</v>
@@ -39522,7 +39638,7 @@
         <v>0.377</v>
       </c>
       <c r="T404" s="7" t="n">
-        <v>16912</v>
+        <v>21184</v>
       </c>
       <c r="U404" s="7" t="n">
         <v>9.164300000000001</v>
@@ -39615,7 +39731,7 @@
         <v>0.273</v>
       </c>
       <c r="T405" s="7" t="n">
-        <v>18749</v>
+        <v>23486</v>
       </c>
       <c r="U405" s="7" t="n">
         <v>7.5619</v>
@@ -39708,7 +39824,7 @@
         <v>0.2234</v>
       </c>
       <c r="T406" s="7" t="n">
-        <v>11606</v>
+        <v>14539</v>
       </c>
       <c r="U406" s="7" t="n">
         <v>7.6963</v>
@@ -39801,7 +39917,7 @@
         <v>0.3254</v>
       </c>
       <c r="T407" s="7" t="n">
-        <v>11411</v>
+        <v>14294</v>
       </c>
       <c r="U407" s="7" t="n">
         <v>4.9129</v>
@@ -39894,7 +40010,7 @@
         <v>0.7244</v>
       </c>
       <c r="T408" s="7" t="n">
-        <v>6213</v>
+        <v>7783</v>
       </c>
       <c r="U408" s="7" t="n">
         <v>2.552</v>
@@ -39987,7 +40103,7 @@
         <v>0.3835</v>
       </c>
       <c r="T409" s="7" t="n">
-        <v>10421</v>
+        <v>13054</v>
       </c>
       <c r="U409" s="7" t="n">
         <v>5.2609</v>
@@ -40080,7 +40196,7 @@
         <v>0.1178</v>
       </c>
       <c r="T410" s="7" t="n">
-        <v>13903</v>
+        <v>17415</v>
       </c>
       <c r="U410" s="7" t="n">
         <v>7.224</v>
@@ -40173,7 +40289,7 @@
         <v>0.0462</v>
       </c>
       <c r="T411" s="7" t="n">
-        <v>16211</v>
+        <v>20306</v>
       </c>
       <c r="U411" s="7" t="n">
         <v>8.4633</v>
@@ -40266,7 +40382,7 @@
         <v>0.3265</v>
       </c>
       <c r="T412" s="7" t="n">
-        <v>20218</v>
+        <v>25325</v>
       </c>
       <c r="U412" s="7" t="n">
         <v>4.4027</v>
@@ -40359,7 +40475,7 @@
         <v>0.2767</v>
       </c>
       <c r="T413" s="7" t="n">
-        <v>13584</v>
+        <v>17016</v>
       </c>
       <c r="U413" s="7" t="n">
         <v>5.849</v>
@@ -40452,7 +40568,7 @@
         <v>0.1632</v>
       </c>
       <c r="T414" s="7" t="n">
-        <v>34599</v>
+        <v>43340</v>
       </c>
       <c r="U414" s="7" t="n">
         <v>6.9352</v>
@@ -40545,7 +40661,7 @@
         <v>0.1397</v>
       </c>
       <c r="T415" s="7" t="n">
-        <v>15226</v>
+        <v>19072</v>
       </c>
       <c r="U415" s="7" t="n">
         <v>7.9121</v>
@@ -40638,7 +40754,7 @@
         <v>0.0876</v>
       </c>
       <c r="T416" s="7" t="n">
-        <v>29539</v>
+        <v>37001</v>
       </c>
       <c r="U416" s="7" t="n">
         <v>6.7975</v>
@@ -40731,7 +40847,7 @@
         <v>0.0336</v>
       </c>
       <c r="T417" s="7" t="n">
-        <v>16354</v>
+        <v>20485</v>
       </c>
       <c r="U417" s="7" t="n">
         <v>7.2435</v>
@@ -40824,7 +40940,7 @@
         <v>0.0344</v>
       </c>
       <c r="T418" s="7" t="n">
-        <v>16062</v>
+        <v>20120</v>
       </c>
       <c r="U418" s="7" t="n">
         <v>7.1149</v>
@@ -40917,7 +41033,7 @@
         <v>0.248</v>
       </c>
       <c r="T419" s="7" t="n">
-        <v>15229</v>
+        <v>19076</v>
       </c>
       <c r="U419" s="7" t="n">
         <v>6.5565</v>
@@ -41010,7 +41126,7 @@
         <v>0.3044</v>
       </c>
       <c r="T420" s="7" t="n">
-        <v>12847</v>
+        <v>16092</v>
       </c>
       <c r="U420" s="7" t="n">
         <v>3.974</v>
@@ -41103,7 +41219,7 @@
         <v>0.0848</v>
       </c>
       <c r="T421" s="7" t="n">
-        <v>12352</v>
+        <v>15472</v>
       </c>
       <c r="U421" s="7" t="n">
         <v>2.7817</v>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>136.7</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L32" s="7" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O32" s="7" t="b">
         <v>0</v>
@@ -43860,19 +43860,19 @@
         </is>
       </c>
       <c r="I447" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J447" s="7" t="n">
         <v>126.1</v>
       </c>
       <c r="K447" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L447" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M447" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M447" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="N447" s="7" t="n">
         <v>0</v>
@@ -43953,19 +43953,19 @@
         </is>
       </c>
       <c r="I448" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J448" s="7" t="n">
         <v>100.8</v>
       </c>
       <c r="K448" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L448" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M448" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N448" s="7" t="n">
         <v>0</v>
@@ -44046,19 +44046,19 @@
         </is>
       </c>
       <c r="I449" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J449" s="7" t="n">
         <v>98.3</v>
       </c>
       <c r="K449" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L449" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M449" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N449" s="7" t="n">
         <v>0</v>
@@ -44139,19 +44139,19 @@
         </is>
       </c>
       <c r="I450" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J450" s="7" t="n">
         <v>132.9</v>
       </c>
       <c r="K450" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L450" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M450" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M450" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="N450" s="7" t="n">
         <v>0</v>
@@ -44232,19 +44232,19 @@
         </is>
       </c>
       <c r="I451" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J451" s="7" t="n">
         <v>128.6</v>
       </c>
       <c r="K451" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L451" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M451" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M451" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="N451" s="7" t="n">
         <v>0</v>
@@ -44325,19 +44325,19 @@
         </is>
       </c>
       <c r="I452" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J452" s="7" t="n">
         <v>116.8</v>
       </c>
       <c r="K452" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L452" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M452" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N452" s="7" t="n">
         <v>0</v>
@@ -44418,19 +44418,19 @@
         </is>
       </c>
       <c r="I453" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J453" s="7" t="n">
         <v>45.8</v>
       </c>
       <c r="K453" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L453" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M453" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N453" s="7" t="n">
         <v>0</v>
@@ -44511,19 +44511,19 @@
         </is>
       </c>
       <c r="I454" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J454" s="7" t="n">
         <v>319.2</v>
       </c>
       <c r="K454" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L454" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M454" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N454" s="7" t="n">
         <v>0</v>
@@ -44701,19 +44701,19 @@
         </is>
       </c>
       <c r="I456" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J456" s="7" t="n">
         <v>76.7</v>
       </c>
       <c r="K456" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L456" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M456" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N456" s="7" t="n">
         <v>0</v>
@@ -44794,19 +44794,19 @@
         </is>
       </c>
       <c r="I457" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J457" s="7" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K457" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L457" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M457" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N457" s="7" t="n">
         <v>0</v>
@@ -44887,19 +44887,19 @@
         </is>
       </c>
       <c r="I458" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J458" s="7" t="n">
         <v>113.5</v>
       </c>
       <c r="K458" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L458" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M458" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N458" s="7" t="n">
         <v>0</v>
@@ -44980,19 +44980,19 @@
         </is>
       </c>
       <c r="I459" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J459" s="7" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="K459" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L459" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M459" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N459" s="7" t="n">
         <v>0</v>
@@ -45073,19 +45073,19 @@
         </is>
       </c>
       <c r="I460" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J460" s="7" t="n">
         <v>84.5</v>
       </c>
       <c r="K460" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L460" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M460" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N460" s="7" t="n">
         <v>0</v>
@@ -45166,19 +45166,19 @@
         </is>
       </c>
       <c r="I461" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J461" s="7" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="K461" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L461" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M461" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N461" s="7" t="n">
         <v>0</v>
@@ -45259,19 +45259,19 @@
         </is>
       </c>
       <c r="I462" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J462" s="7" t="n">
         <v>121.7</v>
       </c>
       <c r="K462" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L462" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M462" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M462" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="N462" s="7" t="n">
         <v>0</v>
@@ -45352,19 +45352,19 @@
         </is>
       </c>
       <c r="I463" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J463" s="7" t="n">
         <v>333.5</v>
       </c>
       <c r="K463" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L463" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M463" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N463" s="7" t="n">
         <v>0</v>
@@ -45445,19 +45445,19 @@
         </is>
       </c>
       <c r="I464" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J464" s="7" t="n">
         <v>221.3</v>
       </c>
       <c r="K464" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L464" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M464" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N464" s="7" t="n">
         <v>0</v>
@@ -45635,19 +45635,19 @@
         </is>
       </c>
       <c r="I466" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J466" s="7" t="n">
         <v>288.5</v>
       </c>
       <c r="K466" s="7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L466" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M466" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N466" s="7" t="n">
         <v>0</v>
@@ -45728,19 +45728,19 @@
         </is>
       </c>
       <c r="I467" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J467" s="7" t="n">
         <v>284.9</v>
       </c>
       <c r="K467" s="7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L467" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M467" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N467" s="7" t="n">
         <v>0</v>
@@ -46209,19 +46209,19 @@
         </is>
       </c>
       <c r="I472" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J472" s="7" t="n">
         <v>106.7</v>
       </c>
       <c r="K472" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L472" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M472" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N472" s="7" t="n">
         <v>0</v>
@@ -46302,19 +46302,19 @@
         </is>
       </c>
       <c r="I473" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J473" s="7" t="n">
         <v>91.5</v>
       </c>
       <c r="K473" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L473" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M473" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N473" s="7" t="n">
         <v>0</v>
@@ -46395,19 +46395,19 @@
         </is>
       </c>
       <c r="I474" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J474" s="7" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="K474" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L474" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M474" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N474" s="7" t="n">
         <v>0</v>
@@ -46488,19 +46488,19 @@
         </is>
       </c>
       <c r="I475" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J475" s="7" t="n">
         <v>85.2</v>
       </c>
       <c r="K475" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L475" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M475" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N475" s="7" t="n">
         <v>0</v>
@@ -46581,19 +46581,19 @@
         </is>
       </c>
       <c r="I476" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J476" s="7" t="n">
         <v>93.7</v>
       </c>
       <c r="K476" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L476" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M476" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N476" s="7" t="n">
         <v>0</v>
@@ -46674,19 +46674,19 @@
         </is>
       </c>
       <c r="I477" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J477" s="7" t="n">
         <v>126.3</v>
       </c>
       <c r="K477" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L477" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M477" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M477" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="N477" s="7" t="n">
         <v>0</v>
@@ -46864,19 +46864,19 @@
         </is>
       </c>
       <c r="I479" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J479" s="7" t="n">
         <v>150</v>
       </c>
       <c r="K479" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L479" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M479" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M479" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N479" s="7" t="n">
         <v>0</v>
@@ -47054,19 +47054,19 @@
         </is>
       </c>
       <c r="I481" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J481" s="7" t="n">
         <v>131.9</v>
       </c>
       <c r="K481" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L481" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M481" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M481" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="N481" s="7" t="n">
         <v>0</v>
@@ -47147,19 +47147,19 @@
         </is>
       </c>
       <c r="I482" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J482" s="7" t="n">
         <v>118.5</v>
       </c>
       <c r="K482" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L482" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M482" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N482" s="7" t="n">
         <v>0</v>
@@ -47240,19 +47240,19 @@
         </is>
       </c>
       <c r="I483" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J483" s="7" t="n">
         <v>213.1</v>
       </c>
       <c r="K483" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L483" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M483" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N483" s="7" t="n">
         <v>0</v>
@@ -47333,19 +47333,19 @@
         </is>
       </c>
       <c r="I484" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J484" s="7" t="n">
         <v>94.09999999999999</v>
       </c>
       <c r="K484" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L484" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M484" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N484" s="7" t="n">
         <v>0</v>
@@ -47426,19 +47426,19 @@
         </is>
       </c>
       <c r="I485" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J485" s="7" t="n">
         <v>104</v>
       </c>
       <c r="K485" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L485" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M485" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N485" s="7" t="n">
         <v>0</v>
@@ -47519,19 +47519,19 @@
         </is>
       </c>
       <c r="I486" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J486" s="7" t="n">
         <v>264.4</v>
       </c>
       <c r="K486" s="7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L486" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M486" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N486" s="7" t="n">
         <v>0</v>
@@ -47612,19 +47612,19 @@
         </is>
       </c>
       <c r="I487" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J487" s="7" t="n">
         <v>232.9</v>
       </c>
       <c r="K487" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L487" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M487" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N487" s="7" t="n">
         <v>0</v>
@@ -47705,19 +47705,19 @@
         </is>
       </c>
       <c r="I488" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J488" s="7" t="n">
         <v>362.5</v>
       </c>
       <c r="K488" s="7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L488" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M488" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N488" s="7" t="n">
         <v>0</v>
@@ -47895,19 +47895,19 @@
         </is>
       </c>
       <c r="I490" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J490" s="7" t="n">
         <v>175.8</v>
       </c>
       <c r="K490" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L490" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M490" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N490" s="7" t="n">
         <v>0</v>
@@ -48275,19 +48275,19 @@
         </is>
       </c>
       <c r="I494" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J494" s="7" t="n">
         <v>182.3</v>
       </c>
       <c r="K494" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L494" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M494" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N494" s="7" t="n">
         <v>0</v>
@@ -48655,19 +48655,19 @@
         </is>
       </c>
       <c r="I498" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J498" s="7" t="n">
         <v>150.1</v>
       </c>
       <c r="K498" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L498" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M498" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M498" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N498" s="7" t="n">
         <v>0</v>
@@ -48845,19 +48845,19 @@
         </is>
       </c>
       <c r="I500" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J500" s="7" t="n">
         <v>189.4</v>
       </c>
       <c r="K500" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L500" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M500" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N500" s="7" t="n">
         <v>0</v>
@@ -48938,19 +48938,19 @@
         </is>
       </c>
       <c r="I501" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J501" s="7" t="n">
         <v>186</v>
       </c>
       <c r="K501" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L501" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M501" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N501" s="7" t="n">
         <v>0</v>
@@ -49031,19 +49031,19 @@
         </is>
       </c>
       <c r="I502" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J502" s="7" t="n">
         <v>168.9</v>
       </c>
       <c r="K502" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L502" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M502" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M502" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N502" s="7" t="n">
         <v>0</v>
@@ -49504,19 +49504,19 @@
         </is>
       </c>
       <c r="I507" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J507" s="7" t="n">
         <v>169.5</v>
       </c>
       <c r="K507" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L507" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M507" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M507" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N507" s="7" t="n">
         <v>0</v>
@@ -50074,19 +50074,19 @@
         </is>
       </c>
       <c r="I513" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J513" s="7" t="n">
         <v>308.9</v>
       </c>
       <c r="K513" s="7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L513" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M513" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N513" s="7" t="n">
         <v>0</v>
@@ -50167,19 +50167,19 @@
         </is>
       </c>
       <c r="I514" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J514" s="7" t="n">
         <v>315.2</v>
       </c>
       <c r="K514" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L514" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M514" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N514" s="7" t="n">
         <v>0</v>
@@ -50551,19 +50551,19 @@
         </is>
       </c>
       <c r="I518" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J518" s="7" t="n">
         <v>145.1</v>
       </c>
       <c r="K518" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L518" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M518" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M518" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N518" s="7" t="n">
         <v>0</v>
@@ -50644,19 +50644,19 @@
         </is>
       </c>
       <c r="I519" s="7" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J519" s="7" t="n">
         <v>173.3</v>
       </c>
       <c r="K519" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L519" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M519" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M519" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N519" s="7" t="n">
         <v>0</v>
@@ -50737,19 +50737,19 @@
         </is>
       </c>
       <c r="I520" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J520" s="7" t="n">
         <v>146.4</v>
       </c>
       <c r="K520" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L520" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M520" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M520" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N520" s="7" t="n">
         <v>0</v>
@@ -50830,19 +50830,19 @@
         </is>
       </c>
       <c r="I521" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J521" s="7" t="n">
         <v>175.6</v>
       </c>
       <c r="K521" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L521" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M521" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N521" s="7" t="n">
         <v>0</v>
@@ -50923,19 +50923,19 @@
         </is>
       </c>
       <c r="I522" s="7" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J522" s="7" t="n">
         <v>186.4</v>
       </c>
       <c r="K522" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L522" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M522" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N522" s="7" t="n">
         <v>0</v>
@@ -51016,19 +51016,19 @@
         </is>
       </c>
       <c r="I523" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J523" s="7" t="n">
         <v>200.5</v>
       </c>
       <c r="K523" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L523" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M523" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N523" s="7" t="n">
         <v>0</v>
@@ -51206,19 +51206,19 @@
         </is>
       </c>
       <c r="I525" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J525" s="7" t="n">
         <v>181.9</v>
       </c>
       <c r="K525" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L525" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M525" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N525" s="7" t="n">
         <v>0</v>
@@ -51299,19 +51299,19 @@
         </is>
       </c>
       <c r="I526" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J526" s="7" t="n">
         <v>201.1</v>
       </c>
       <c r="K526" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L526" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M526" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N526" s="7" t="n">
         <v>0</v>
@@ -51392,19 +51392,19 @@
         </is>
       </c>
       <c r="I527" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J527" s="7" t="n">
         <v>207.5</v>
       </c>
       <c r="K527" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L527" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M527" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N527" s="7" t="n">
         <v>0</v>
@@ -51485,19 +51485,19 @@
         </is>
       </c>
       <c r="I528" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J528" s="7" t="n">
         <v>194.8</v>
       </c>
       <c r="K528" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L528" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M528" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N528" s="7" t="n">
         <v>0</v>
@@ -52144,19 +52144,19 @@
         </is>
       </c>
       <c r="I535" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J535" s="7" t="n">
         <v>121.9</v>
       </c>
       <c r="K535" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L535" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M535" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M535" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="N535" s="7" t="n">
         <v>0</v>
@@ -52237,19 +52237,19 @@
         </is>
       </c>
       <c r="I536" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J536" s="7" t="n">
         <v>151.1</v>
       </c>
       <c r="K536" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L536" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M536" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M536" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N536" s="7" t="n">
         <v>0</v>
@@ -52621,19 +52621,19 @@
         </is>
       </c>
       <c r="I540" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J540" s="7" t="n">
         <v>134.9</v>
       </c>
       <c r="K540" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L540" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M540" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M540" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="N540" s="7" t="n">
         <v>0</v>
@@ -52811,19 +52811,19 @@
         </is>
       </c>
       <c r="I542" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J542" s="7" t="n">
         <v>177.9</v>
       </c>
       <c r="K542" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L542" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M542" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N542" s="7" t="n">
         <v>0</v>
@@ -53870,19 +53870,19 @@
         </is>
       </c>
       <c r="I553" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J553" s="7" t="n">
         <v>168.3</v>
       </c>
       <c r="K553" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L553" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M553" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M553" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="N553" s="7" t="n">
         <v>0</v>
@@ -53963,19 +53963,19 @@
         </is>
       </c>
       <c r="I554" s="7" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="J554" s="7" t="n">
         <v>195.7</v>
       </c>
       <c r="K554" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L554" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M554" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N554" s="7" t="n">
         <v>0</v>
@@ -54343,19 +54343,19 @@
         </is>
       </c>
       <c r="I558" s="7" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J558" s="7" t="n">
         <v>241.4</v>
       </c>
       <c r="K558" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L558" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M558" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N558" s="7" t="n">
         <v>0</v>
@@ -54436,19 +54436,19 @@
         </is>
       </c>
       <c r="I559" s="7" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J559" s="7" t="n">
         <v>221.2</v>
       </c>
       <c r="K559" s="7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L559" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M559" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N559" s="7" t="n">
         <v>0</v>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>136.7</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="7" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O32" s="7" t="b">
         <v>0</v>
@@ -43860,16 +43860,16 @@
         </is>
       </c>
       <c r="I447" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J447" s="7" t="n">
         <v>126.1</v>
       </c>
       <c r="K447" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L447" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M447" s="7" t="n">
         <v>2</v>
@@ -43953,19 +43953,19 @@
         </is>
       </c>
       <c r="I448" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J448" s="7" t="n">
         <v>100.8</v>
       </c>
       <c r="K448" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L448" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L448" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M448" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N448" s="7" t="n">
         <v>0</v>
@@ -44046,19 +44046,19 @@
         </is>
       </c>
       <c r="I449" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J449" s="7" t="n">
         <v>98.3</v>
       </c>
       <c r="K449" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L449" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M449" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N449" s="7" t="n">
         <v>0</v>
@@ -44139,16 +44139,16 @@
         </is>
       </c>
       <c r="I450" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J450" s="7" t="n">
         <v>132.9</v>
       </c>
       <c r="K450" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L450" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M450" s="7" t="n">
         <v>2</v>
@@ -44232,16 +44232,16 @@
         </is>
       </c>
       <c r="I451" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J451" s="7" t="n">
         <v>128.6</v>
       </c>
       <c r="K451" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L451" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M451" s="7" t="n">
         <v>2</v>
@@ -44325,19 +44325,19 @@
         </is>
       </c>
       <c r="I452" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J452" s="7" t="n">
         <v>116.8</v>
       </c>
       <c r="K452" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L452" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L452" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M452" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N452" s="7" t="n">
         <v>0</v>
@@ -44418,7 +44418,7 @@
         </is>
       </c>
       <c r="I453" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J453" s="7" t="n">
         <v>45.8</v>
@@ -44511,19 +44511,19 @@
         </is>
       </c>
       <c r="I454" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J454" s="7" t="n">
         <v>319.2</v>
       </c>
       <c r="K454" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L454" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M454" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N454" s="7" t="n">
         <v>0</v>
@@ -44701,19 +44701,19 @@
         </is>
       </c>
       <c r="I456" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J456" s="7" t="n">
         <v>76.7</v>
       </c>
       <c r="K456" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L456" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M456" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N456" s="7" t="n">
         <v>0</v>
@@ -44794,19 +44794,19 @@
         </is>
       </c>
       <c r="I457" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J457" s="7" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K457" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L457" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M457" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N457" s="7" t="n">
         <v>0</v>
@@ -44887,19 +44887,19 @@
         </is>
       </c>
       <c r="I458" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J458" s="7" t="n">
         <v>113.5</v>
       </c>
       <c r="K458" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L458" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L458" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M458" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N458" s="7" t="n">
         <v>0</v>
@@ -44980,19 +44980,19 @@
         </is>
       </c>
       <c r="I459" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J459" s="7" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="K459" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L459" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M459" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N459" s="7" t="n">
         <v>0</v>
@@ -45073,19 +45073,19 @@
         </is>
       </c>
       <c r="I460" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J460" s="7" t="n">
         <v>84.5</v>
       </c>
       <c r="K460" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L460" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M460" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N460" s="7" t="n">
         <v>0</v>
@@ -45166,19 +45166,19 @@
         </is>
       </c>
       <c r="I461" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J461" s="7" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="K461" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L461" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M461" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N461" s="7" t="n">
         <v>0</v>
@@ -45259,16 +45259,16 @@
         </is>
       </c>
       <c r="I462" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J462" s="7" t="n">
         <v>121.7</v>
       </c>
       <c r="K462" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L462" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M462" s="7" t="n">
         <v>2</v>
@@ -45352,19 +45352,19 @@
         </is>
       </c>
       <c r="I463" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J463" s="7" t="n">
         <v>333.5</v>
       </c>
       <c r="K463" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L463" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M463" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N463" s="7" t="n">
         <v>0</v>
@@ -45445,19 +45445,19 @@
         </is>
       </c>
       <c r="I464" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J464" s="7" t="n">
         <v>221.3</v>
       </c>
       <c r="K464" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L464" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M464" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N464" s="7" t="n">
         <v>0</v>
@@ -45635,19 +45635,19 @@
         </is>
       </c>
       <c r="I466" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J466" s="7" t="n">
         <v>288.5</v>
       </c>
       <c r="K466" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L466" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M466" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="L466" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M466" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N466" s="7" t="n">
         <v>0</v>
@@ -45728,19 +45728,19 @@
         </is>
       </c>
       <c r="I467" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J467" s="7" t="n">
         <v>284.9</v>
       </c>
       <c r="K467" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L467" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M467" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="L467" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M467" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N467" s="7" t="n">
         <v>0</v>
@@ -46209,19 +46209,19 @@
         </is>
       </c>
       <c r="I472" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J472" s="7" t="n">
         <v>106.7</v>
       </c>
       <c r="K472" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L472" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L472" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M472" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N472" s="7" t="n">
         <v>0</v>
@@ -46302,19 +46302,19 @@
         </is>
       </c>
       <c r="I473" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J473" s="7" t="n">
         <v>91.5</v>
       </c>
       <c r="K473" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L473" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M473" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N473" s="7" t="n">
         <v>0</v>
@@ -46395,19 +46395,19 @@
         </is>
       </c>
       <c r="I474" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J474" s="7" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="K474" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L474" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M474" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N474" s="7" t="n">
         <v>0</v>
@@ -46488,19 +46488,19 @@
         </is>
       </c>
       <c r="I475" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J475" s="7" t="n">
         <v>85.2</v>
       </c>
       <c r="K475" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L475" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M475" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N475" s="7" t="n">
         <v>0</v>
@@ -46581,19 +46581,19 @@
         </is>
       </c>
       <c r="I476" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J476" s="7" t="n">
         <v>93.7</v>
       </c>
       <c r="K476" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L476" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M476" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N476" s="7" t="n">
         <v>0</v>
@@ -46674,16 +46674,16 @@
         </is>
       </c>
       <c r="I477" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J477" s="7" t="n">
         <v>126.3</v>
       </c>
       <c r="K477" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L477" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M477" s="7" t="n">
         <v>2</v>
@@ -46864,16 +46864,16 @@
         </is>
       </c>
       <c r="I479" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J479" s="7" t="n">
         <v>150</v>
       </c>
       <c r="K479" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L479" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M479" s="7" t="n">
         <v>2</v>
@@ -47054,16 +47054,16 @@
         </is>
       </c>
       <c r="I481" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J481" s="7" t="n">
         <v>131.9</v>
       </c>
       <c r="K481" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L481" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M481" s="7" t="n">
         <v>2</v>
@@ -47147,19 +47147,19 @@
         </is>
       </c>
       <c r="I482" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J482" s="7" t="n">
         <v>118.5</v>
       </c>
       <c r="K482" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L482" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L482" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M482" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N482" s="7" t="n">
         <v>0</v>
@@ -47240,19 +47240,19 @@
         </is>
       </c>
       <c r="I483" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J483" s="7" t="n">
         <v>213.1</v>
       </c>
       <c r="K483" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L483" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M483" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N483" s="7" t="n">
         <v>0</v>
@@ -47333,19 +47333,19 @@
         </is>
       </c>
       <c r="I484" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J484" s="7" t="n">
         <v>94.09999999999999</v>
       </c>
       <c r="K484" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L484" s="7" t="n">
         <v>1</v>
       </c>
       <c r="M484" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N484" s="7" t="n">
         <v>0</v>
@@ -47426,19 +47426,19 @@
         </is>
       </c>
       <c r="I485" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J485" s="7" t="n">
         <v>104</v>
       </c>
       <c r="K485" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L485" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L485" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M485" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N485" s="7" t="n">
         <v>0</v>
@@ -47519,19 +47519,19 @@
         </is>
       </c>
       <c r="I486" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J486" s="7" t="n">
         <v>264.4</v>
       </c>
       <c r="K486" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L486" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M486" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="L486" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M486" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N486" s="7" t="n">
         <v>0</v>
@@ -47612,19 +47612,19 @@
         </is>
       </c>
       <c r="I487" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J487" s="7" t="n">
         <v>232.9</v>
       </c>
       <c r="K487" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L487" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M487" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N487" s="7" t="n">
         <v>0</v>
@@ -47705,19 +47705,19 @@
         </is>
       </c>
       <c r="I488" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J488" s="7" t="n">
         <v>362.5</v>
       </c>
       <c r="K488" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L488" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M488" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N488" s="7" t="n">
         <v>0</v>
@@ -47895,19 +47895,19 @@
         </is>
       </c>
       <c r="I490" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J490" s="7" t="n">
         <v>175.8</v>
       </c>
       <c r="K490" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L490" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M490" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L490" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M490" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N490" s="7" t="n">
         <v>0</v>
@@ -48275,19 +48275,19 @@
         </is>
       </c>
       <c r="I494" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J494" s="7" t="n">
         <v>182.3</v>
       </c>
       <c r="K494" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L494" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M494" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L494" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M494" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N494" s="7" t="n">
         <v>0</v>
@@ -48655,19 +48655,19 @@
         </is>
       </c>
       <c r="I498" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J498" s="7" t="n">
         <v>150.1</v>
       </c>
       <c r="K498" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L498" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M498" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L498" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M498" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N498" s="7" t="n">
         <v>0</v>
@@ -48845,19 +48845,19 @@
         </is>
       </c>
       <c r="I500" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J500" s="7" t="n">
         <v>189.4</v>
       </c>
       <c r="K500" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L500" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M500" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L500" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M500" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N500" s="7" t="n">
         <v>0</v>
@@ -48938,19 +48938,19 @@
         </is>
       </c>
       <c r="I501" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J501" s="7" t="n">
         <v>186</v>
       </c>
       <c r="K501" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L501" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M501" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L501" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M501" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N501" s="7" t="n">
         <v>0</v>
@@ -49031,19 +49031,19 @@
         </is>
       </c>
       <c r="I502" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J502" s="7" t="n">
         <v>168.9</v>
       </c>
       <c r="K502" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L502" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M502" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L502" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M502" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N502" s="7" t="n">
         <v>0</v>
@@ -49504,19 +49504,19 @@
         </is>
       </c>
       <c r="I507" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J507" s="7" t="n">
         <v>169.5</v>
       </c>
       <c r="K507" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L507" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M507" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L507" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M507" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N507" s="7" t="n">
         <v>0</v>
@@ -50074,19 +50074,19 @@
         </is>
       </c>
       <c r="I513" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J513" s="7" t="n">
         <v>308.9</v>
       </c>
       <c r="K513" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L513" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M513" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N513" s="7" t="n">
         <v>0</v>
@@ -50167,19 +50167,19 @@
         </is>
       </c>
       <c r="I514" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J514" s="7" t="n">
         <v>315.2</v>
       </c>
       <c r="K514" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L514" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M514" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N514" s="7" t="n">
         <v>0</v>
@@ -50551,16 +50551,16 @@
         </is>
       </c>
       <c r="I518" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J518" s="7" t="n">
         <v>145.1</v>
       </c>
       <c r="K518" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L518" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M518" s="7" t="n">
         <v>2</v>
@@ -50644,19 +50644,19 @@
         </is>
       </c>
       <c r="I519" s="7" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="J519" s="7" t="n">
         <v>173.3</v>
       </c>
       <c r="K519" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L519" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M519" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L519" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M519" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N519" s="7" t="n">
         <v>0</v>
@@ -50737,16 +50737,16 @@
         </is>
       </c>
       <c r="I520" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J520" s="7" t="n">
         <v>146.4</v>
       </c>
       <c r="K520" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L520" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M520" s="7" t="n">
         <v>2</v>
@@ -50830,19 +50830,19 @@
         </is>
       </c>
       <c r="I521" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J521" s="7" t="n">
         <v>175.6</v>
       </c>
       <c r="K521" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L521" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M521" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L521" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M521" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N521" s="7" t="n">
         <v>0</v>
@@ -50923,19 +50923,19 @@
         </is>
       </c>
       <c r="I522" s="7" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="J522" s="7" t="n">
         <v>186.4</v>
       </c>
       <c r="K522" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L522" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M522" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N522" s="7" t="n">
         <v>0</v>
@@ -51016,19 +51016,19 @@
         </is>
       </c>
       <c r="I523" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J523" s="7" t="n">
         <v>200.5</v>
       </c>
       <c r="K523" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L523" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M523" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N523" s="7" t="n">
         <v>0</v>
@@ -51206,19 +51206,19 @@
         </is>
       </c>
       <c r="I525" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J525" s="7" t="n">
         <v>181.9</v>
       </c>
       <c r="K525" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L525" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M525" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L525" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M525" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N525" s="7" t="n">
         <v>0</v>
@@ -51299,19 +51299,19 @@
         </is>
       </c>
       <c r="I526" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J526" s="7" t="n">
         <v>201.1</v>
       </c>
       <c r="K526" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L526" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M526" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N526" s="7" t="n">
         <v>0</v>
@@ -51392,19 +51392,19 @@
         </is>
       </c>
       <c r="I527" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J527" s="7" t="n">
         <v>207.5</v>
       </c>
       <c r="K527" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L527" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M527" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N527" s="7" t="n">
         <v>0</v>
@@ -51485,19 +51485,19 @@
         </is>
       </c>
       <c r="I528" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J528" s="7" t="n">
         <v>194.8</v>
       </c>
       <c r="K528" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L528" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M528" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L528" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M528" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N528" s="7" t="n">
         <v>0</v>
@@ -52144,16 +52144,16 @@
         </is>
       </c>
       <c r="I535" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J535" s="7" t="n">
         <v>121.9</v>
       </c>
       <c r="K535" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L535" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M535" s="7" t="n">
         <v>2</v>
@@ -52237,19 +52237,19 @@
         </is>
       </c>
       <c r="I536" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J536" s="7" t="n">
         <v>151.1</v>
       </c>
       <c r="K536" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L536" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M536" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L536" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M536" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N536" s="7" t="n">
         <v>0</v>
@@ -52621,16 +52621,16 @@
         </is>
       </c>
       <c r="I540" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J540" s="7" t="n">
         <v>134.9</v>
       </c>
       <c r="K540" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L540" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M540" s="7" t="n">
         <v>2</v>
@@ -52811,19 +52811,19 @@
         </is>
       </c>
       <c r="I542" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J542" s="7" t="n">
         <v>177.9</v>
       </c>
       <c r="K542" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L542" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M542" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L542" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M542" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N542" s="7" t="n">
         <v>0</v>
@@ -53870,19 +53870,19 @@
         </is>
       </c>
       <c r="I553" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J553" s="7" t="n">
         <v>168.3</v>
       </c>
       <c r="K553" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L553" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M553" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L553" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M553" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N553" s="7" t="n">
         <v>0</v>
@@ -53963,19 +53963,19 @@
         </is>
       </c>
       <c r="I554" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J554" s="7" t="n">
         <v>195.7</v>
       </c>
       <c r="K554" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L554" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M554" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="L554" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M554" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="N554" s="7" t="n">
         <v>0</v>
@@ -54343,7 +54343,7 @@
         </is>
       </c>
       <c r="I558" s="7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J558" s="7" t="n">
         <v>241.4</v>
@@ -54436,19 +54436,19 @@
         </is>
       </c>
       <c r="I559" s="7" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="J559" s="7" t="n">
         <v>221.2</v>
       </c>
       <c r="K559" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L559" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M559" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N559" s="7" t="n">
         <v>0</v>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.xlsx
@@ -20948,7 +20948,7 @@
         </is>
       </c>
       <c r="D216" s="7" t="n">
-        <v>6.5</v>
+        <v>6.356</v>
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>35</v>
       </c>
       <c r="J216" s="7" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
       <c r="K216" s="7" t="n">
         <v>3</v>
@@ -21003,7 +21003,7 @@
         <v>6671</v>
       </c>
       <c r="U216" s="7" t="n">
-        <v>759</v>
+        <v>532.2</v>
       </c>
       <c r="V216" s="7" t="n">
         <v>5</v>
@@ -21017,10 +21017,10 @@
         </is>
       </c>
       <c r="Y216" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z216" s="7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217">
@@ -60728,7 +60728,7 @@
         </is>
       </c>
       <c r="D642" s="7" t="n">
-        <v>54.466</v>
+        <v>37.093</v>
       </c>
       <c r="E642" s="7" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         <v>15</v>
       </c>
       <c r="J642" s="7" t="n">
-        <v>163.4</v>
+        <v>111.3</v>
       </c>
       <c r="K642" s="7" t="n">
         <v>13</v>
@@ -60783,7 +60783,7 @@
         <v>11716</v>
       </c>
       <c r="U642" s="7" t="n">
-        <v>3765.4</v>
+        <v>2363.7</v>
       </c>
       <c r="V642" s="7" t="n">
         <v>8</v>
@@ -60797,10 +60797,10 @@
         </is>
       </c>
       <c r="Y642" s="7" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="Z642" s="7" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="643">
